--- a/Validador_Registro.xlsx
+++ b/Validador_Registro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\www\Validador2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFDE4FF-C660-4699-87FB-D682FE253416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF51AD3-5664-4CF4-A89D-4D87A30566DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1440,7 +1440,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1451,7 +1450,7 @@
     <col min="5" max="5" width="14.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.875" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="23.625" customWidth="1"/>
     <col min="9" max="9" width="100.875" style="3" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
@@ -1488,7 +1487,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1517,7 +1516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1546,7 +1545,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1575,7 +1574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1604,7 +1603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1633,7 +1632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1662,7 +1661,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1691,7 +1690,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1720,7 +1719,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1749,7 +1748,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1778,7 +1777,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1807,7 +1806,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -1836,7 +1835,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -1865,7 +1864,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -1894,7 +1893,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -1923,7 +1922,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -1952,7 +1951,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -2010,7 +2009,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -2039,7 +2038,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -2068,7 +2067,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -2097,7 +2096,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>77</v>
       </c>
@@ -2126,7 +2125,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>85</v>
       </c>
@@ -2184,7 +2183,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>90</v>
       </c>
@@ -2213,7 +2212,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>94</v>
       </c>
@@ -2242,7 +2241,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>97</v>
       </c>
@@ -2271,7 +2270,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>101</v>
       </c>
@@ -2300,7 +2299,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>105</v>
       </c>
@@ -2329,7 +2328,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>110</v>
       </c>
@@ -2358,7 +2357,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>114</v>
       </c>
@@ -2387,7 +2386,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -2416,7 +2415,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>121</v>
       </c>
@@ -2445,7 +2444,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>125</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>130</v>
       </c>
@@ -2503,7 +2502,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>134</v>
       </c>
@@ -2532,7 +2531,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>138</v>
       </c>
@@ -2561,7 +2560,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>142</v>
       </c>
@@ -2590,7 +2589,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>146</v>
       </c>
@@ -2619,7 +2618,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>154</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>158</v>
       </c>
@@ -2706,7 +2705,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>162</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>166</v>
       </c>
@@ -2764,7 +2763,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>170</v>
       </c>
@@ -2793,7 +2792,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>174</v>
       </c>
@@ -2822,7 +2821,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>178</v>
       </c>
@@ -2851,7 +2850,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>183</v>
       </c>
@@ -2880,7 +2879,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>187</v>
       </c>
@@ -2909,7 +2908,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>191</v>
       </c>
@@ -2938,7 +2937,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>195</v>
       </c>
@@ -2967,7 +2966,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>199</v>
       </c>
@@ -2996,7 +2995,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>204</v>
       </c>
@@ -3025,7 +3024,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>208</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>212</v>
       </c>
@@ -3083,7 +3082,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>217</v>
       </c>
@@ -3112,7 +3111,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>221</v>
       </c>
@@ -3141,7 +3140,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>224</v>
       </c>
@@ -3170,7 +3169,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>228</v>
       </c>
@@ -3199,7 +3198,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>231</v>
       </c>
@@ -3228,7 +3227,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>235</v>
       </c>
@@ -3257,7 +3256,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>239</v>
       </c>
@@ -3286,7 +3285,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>243</v>
       </c>
@@ -3315,7 +3314,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>246</v>
       </c>
@@ -3344,7 +3343,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>249</v>
       </c>
@@ -3373,7 +3372,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>252</v>
       </c>
@@ -3402,7 +3401,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>255</v>
       </c>
@@ -3553,7 +3552,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>272</v>
       </c>
@@ -3582,7 +3581,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>276</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>279</v>
       </c>
@@ -3640,7 +3639,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>283</v>
       </c>
@@ -3669,7 +3668,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>286</v>
       </c>
@@ -3698,7 +3697,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>289</v>
       </c>
@@ -3727,7 +3726,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>292</v>
       </c>
@@ -3756,7 +3755,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>297</v>
       </c>
@@ -3785,7 +3784,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>301</v>
       </c>
@@ -3814,7 +3813,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>305</v>
       </c>
@@ -3843,7 +3842,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>308</v>
       </c>
@@ -3872,7 +3871,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>312</v>
       </c>
@@ -3901,7 +3900,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>315</v>
       </c>
@@ -3930,7 +3929,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>318</v>
       </c>
@@ -3959,7 +3958,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>322</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>326</v>
       </c>
@@ -4017,7 +4016,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>329</v>
       </c>
@@ -4046,7 +4045,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>333</v>
       </c>
@@ -4075,7 +4074,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>336</v>
       </c>
@@ -4105,18 +4104,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I91" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="A08"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="hospital.json"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I91" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:I91" numberStoredAsText="1"/>

--- a/Validador_Registro.xlsx
+++ b/Validador_Registro.xlsx
@@ -528,7 +528,7 @@
         <v>A28</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -552,7 +552,7 @@
         <v>TOTAL</v>
       </c>
       <c r="B17">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -641,7 +641,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | D16, D17. La expresión indica que [D16+D17] la celda debe contener datos.</v>
+        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | D16, D17 | La expresión indica que [D16+D17] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I2" t="str">
         <v>Códigos: 123000, 123100, 123101, 123102</v>
@@ -742,7 +742,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | B13, C30. La expresión indica que [B13:C30] la celda debe contener datos.</v>
+        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | B13, C30 | La expresión indica que [B13:C30] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I2" t="str">
         <v>Códigos: 123000, 123100</v>
@@ -780,7 +780,7 @@
         <v>ERROR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | C144, P148. La expresión indica que [C144:P148] la celda debe contener datos.</v>
+        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | C144, P148 | La expresión indica que [C144:P148] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I3" t="str">
         <v>Códigos: 123000, 123100</v>
@@ -818,7 +818,7 @@
         <v>ERROR</v>
       </c>
       <c r="H4" t="str">
-        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | C152, P156. La expresión indica que [C152:P156] la celda debe contener datos.</v>
+        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | C152, P156 | La expresión indica que [C152:P156] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I4" t="str">
         <v>Códigos: 123000, 123100</v>
@@ -856,7 +856,7 @@
         <v>ERROR</v>
       </c>
       <c r="H5" t="str">
-        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | C161, D183. La expresión indica que [C161:D183] la celda debe contener datos.</v>
+        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | C161, D183 | La expresión indica que [C161:D183] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I5" t="str">
         <v>Códigos: 123000, 123100</v>
@@ -948,7 +948,7 @@
         <v>C129:C148</v>
       </c>
       <c r="E2" t="str">
-        <v>==</v>
+        <v>&lt;=</v>
       </c>
       <c r="F2" t="str">
         <v>O129:O148</v>
@@ -957,7 +957,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | C129, C148, O129, O148. La expresión indica que [C129:C148] debe ser igual a [O129:O148].</v>
+        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | C129, C148 | REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | O129, O148. La expresión indica que [C129:C148] debe ser menor o igual a [O129:O148].</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -966,10 +966,10 @@
         <v>-</v>
       </c>
       <c r="K2" t="str">
-        <v>-</v>
+        <v>Omitir si exp1=0</v>
       </c>
       <c r="L2" t="str">
-        <v>Compara [C129:C148] sea igual a la suma del rango [O129:O148].</v>
+        <v>Compara [C129:C148] sea menor o igual a la suma del rango [O129:O148]. | Se omite si expresión_1 es 0</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1058,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | B11, E11, I11. La expresión indica que [B11] debe ser igual a [E11:I11].</v>
+        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | B11 | REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | E11, I11. La expresión indica que [B11] debe ser igual a [E11:I11].</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -1150,7 +1150,7 @@
         <v>D53</v>
       </c>
       <c r="E2" t="str">
-        <v>==</v>
+        <v>&gt;=</v>
       </c>
       <c r="F2" t="str">
         <v>D98</v>
@@ -1159,7 +1159,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | D53. La expresión indica que [D53] debe ser igual a [D98].</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | D53 | REM A27 | SECCIÓN B: ACTIVIDADES DE EDUCACIÓN PARA LA SALUD SEGÚN PERSONAL QUE LAS REALIZA (SESIONES) | D98. La expresión indica que [D53] debe ser mayor o igual a [D98].</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -1171,7 +1171,7 @@
         <v>Omitir si exp1=0</v>
       </c>
       <c r="L2" t="str">
-        <v>Compara [D53] sea igual a [D98]. | Se omite si expresión_1 es 0</v>
+        <v>Compara [D53] sea mayor o igual a [D98]. | Se omite si expresión_1 es 0</v>
       </c>
     </row>
     <row r="3">
@@ -1188,7 +1188,7 @@
         <v>D23</v>
       </c>
       <c r="E3" t="str">
-        <v>==</v>
+        <v>&gt;=</v>
       </c>
       <c r="F3" t="str">
         <v>Y23:AA23</v>
@@ -1197,7 +1197,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | D23. La expresión indica que [D23] debe ser igual a [Y23:AA23].</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | D23 | REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Y23, AA23. La expresión indica que [D23] debe ser mayor o igual a [Y23:AA23].</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -1209,7 +1209,7 @@
         <v>Omitir si exp1=0</v>
       </c>
       <c r="L3" t="str">
-        <v>Compara [D23] sea igual a la suma del rango [Y23:AA23]. | Se omite si expresión_1 es 0</v>
+        <v>Compara [D23] sea mayor o igual a la suma del rango [Y23:AA23]. | Se omite si expresión_1 es 0</v>
       </c>
     </row>
   </sheetData>
@@ -1221,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1298,7 +1298,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13, B61. La expresión indica que [B13] debe ser menor o igual a [B61].</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13 | REM A28 | SECCIÓN A.3: EVALUACIÓN INICIAL | B61. La expresión indica que [B13] debe ser menor o igual a [B61].</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -1336,7 +1336,7 @@
         <v>ERROR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13, B14. La expresión indica que [B13] debe ser mayor o igual a [B14].</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13 | REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B14. La expresión indica que [B13] debe ser mayor o igual a [B14].</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -1374,7 +1374,7 @@
         <v>ERROR</v>
       </c>
       <c r="H4" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13, B15. La expresión indica que [B13] debe ser mayor o igual a [B15].</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13 | REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B15. La expresión indica que [B13] debe ser mayor o igual a [B15].</v>
       </c>
       <c r="I4" t="str">
         <v>-</v>
@@ -1412,7 +1412,7 @@
         <v>ERROR</v>
       </c>
       <c r="H5" t="str">
-        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | B29, B30, B52. La expresión indica que [B29] debe ser menor o igual a [B30:B52].</v>
+        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | B29 | REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | B30, B52. La expresión indica que [B29] debe ser menor o igual a [B30:B52].</v>
       </c>
       <c r="I5" t="str">
         <v>-</v>
@@ -1450,7 +1450,7 @@
         <v>ERROR</v>
       </c>
       <c r="H6" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | B149, B150, B177. La expresión indica que [B149] debe ser menor o igual a [B150:B177].</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | B149 | REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | B150, B177. La expresión indica que [B149] debe ser menor o igual a [B150:B177].</v>
       </c>
       <c r="I6" t="str">
         <v>-</v>
@@ -1476,10 +1476,10 @@
         <v>CELDA</v>
       </c>
       <c r="D7" t="str">
-        <v>AM150:AM178</v>
+        <v>AM149:AM177</v>
       </c>
       <c r="E7" t="str">
-        <v>==</v>
+        <v>&gt;=</v>
       </c>
       <c r="F7" t="str">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>REVISAR</v>
       </c>
       <c r="H7" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | AM150, AM178. La expresión indica que [AM150:AM178] la celda no debe contener datos.</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | AM149, AM177 | La expresión indica que [AM149:AM177] debe ser mayor o igual a [0].</v>
       </c>
       <c r="I7" t="str">
-        <v>-</v>
+        <v>Códigos: 123100, 123101, 123102</v>
       </c>
       <c r="J7" t="str">
         <v>-</v>
@@ -1500,12 +1500,50 @@
         <v>-</v>
       </c>
       <c r="L7" t="str">
-        <v>Verifica que la expresión [AM150:AM178] NO contenga datos (sea cero o vacía).</v>
+        <v>Compara [AM149:AM177] sea mayor o igual a 0. | Solo aplica a códigos: 123100, 123101, 123102</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>A28-VAL007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>A28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>CELDA</v>
+      </c>
+      <c r="D8" t="str">
+        <v>AM149:AM177</v>
+      </c>
+      <c r="E8" t="str">
+        <v>!=</v>
+      </c>
+      <c r="F8" t="str">
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="H8" t="str">
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | AM149, AM177 | La expresión indica que [AM149:AM177] la celda debe contener datos (distinto de cero).</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Códigos: 123100, 123101, 123102</v>
+      </c>
+      <c r="J8" t="str">
+        <v>-</v>
+      </c>
+      <c r="K8" t="str">
+        <v>-</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Verifica que la expresión [AM149:AM177] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123100, 123101, 123102</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1580,7 +1618,7 @@
         <v>O12:P12</v>
       </c>
       <c r="E2" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F2" t="str">
         <v>0</v>
@@ -1589,7 +1627,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | O12, P12. La expresión indica que [O12:P12] la celda no debe contener datos.</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | O12, P12 | La expresión indica que [O12:P12] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -1601,7 +1639,7 @@
         <v>-</v>
       </c>
       <c r="L2" t="str">
-        <v>Verifica que la expresión [O12:P12] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [O12:P12] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="3">
@@ -1618,7 +1656,7 @@
         <v>M13:N13</v>
       </c>
       <c r="E3" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F3" t="str">
         <v>0</v>
@@ -1627,7 +1665,7 @@
         <v>ERROR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | M13, N13. La expresión indica que [M13:N13] la celda no debe contener datos.</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | M13, N13 | La expresión indica que [M13:N13] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -1639,7 +1677,7 @@
         <v>-</v>
       </c>
       <c r="L3" t="str">
-        <v>Verifica que la expresión [M13:N13] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [M13:N13] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
   </sheetData>
@@ -1707,7 +1745,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>A30-VAL001</v>
+        <v>A30R-VAL001</v>
       </c>
       <c r="B2" t="str">
         <v>A30R</v>
@@ -1719,7 +1757,7 @@
         <v>B16:B17</v>
       </c>
       <c r="E2" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F2" t="str">
         <v>0</v>
@@ -1728,7 +1766,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A30R | Sección Desconocida | B16, B17. La expresión indica que [B16:B17] la celda no debe contener datos.</v>
+        <v>REM A30R | Sección Desconocida | B16, B17 | La expresión indica que [B16:B17] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -1740,7 +1778,7 @@
         <v>-</v>
       </c>
       <c r="L2" t="str">
-        <v>Verifica que la expresión [B16:B17] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [B16:B17] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
   </sheetData>
@@ -1752,7 +1790,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -2162,7 +2200,7 @@
         <v>F11</v>
       </c>
       <c r="E11" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F11" t="str">
         <v>0</v>
@@ -2171,7 +2209,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H11" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | F11. La expresión indica que [F11] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | F11 | La expresión indica que [F11] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I11" t="str">
         <v>-</v>
@@ -2183,7 +2221,7 @@
         <v>-</v>
       </c>
       <c r="L11" t="str">
-        <v>Verifica que la expresión [F11] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [F11] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="12">
@@ -2200,7 +2238,7 @@
         <v>F12</v>
       </c>
       <c r="E12" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F12" t="str">
         <v>0</v>
@@ -2209,7 +2247,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H12" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | F12. La expresión indica que [F12] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | F12 | La expresión indica que [F12] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I12" t="str">
         <v>-</v>
@@ -2221,7 +2259,7 @@
         <v>-</v>
       </c>
       <c r="L12" t="str">
-        <v>Verifica que la expresión [F12] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [F12] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="13">
@@ -2238,7 +2276,7 @@
         <v>M11</v>
       </c>
       <c r="E13" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F13" t="str">
         <v>0</v>
@@ -2247,7 +2285,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H13" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | M11. La expresión indica que [M11] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | M11 | La expresión indica que [M11] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I13" t="str">
         <v>-</v>
@@ -2259,7 +2297,7 @@
         <v>-</v>
       </c>
       <c r="L13" t="str">
-        <v>Verifica que la expresión [M11] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [M11] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="14">
@@ -2276,7 +2314,7 @@
         <v>M12</v>
       </c>
       <c r="E14" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F14" t="str">
         <v>0</v>
@@ -2285,7 +2323,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H14" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | M12. La expresión indica que [M12] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | M12 | La expresión indica que [M12] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I14" t="str">
         <v>-</v>
@@ -2297,7 +2335,7 @@
         <v>-</v>
       </c>
       <c r="L14" t="str">
-        <v>Verifica que la expresión [M12] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [M12] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="15">
@@ -2314,7 +2352,7 @@
         <v>N11</v>
       </c>
       <c r="E15" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F15" t="str">
         <v>0</v>
@@ -2323,7 +2361,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H15" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N11. La expresión indica que [N11] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N11 | La expresión indica que [N11] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I15" t="str">
         <v>-</v>
@@ -2335,7 +2373,7 @@
         <v>-</v>
       </c>
       <c r="L15" t="str">
-        <v>Verifica que la expresión [N11] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N11] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="16">
@@ -2352,7 +2390,7 @@
         <v>N12</v>
       </c>
       <c r="E16" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F16" t="str">
         <v>0</v>
@@ -2361,7 +2399,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H16" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N12. La expresión indica que [N12] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N12 | La expresión indica que [N12] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I16" t="str">
         <v>-</v>
@@ -2373,7 +2411,7 @@
         <v>-</v>
       </c>
       <c r="L16" t="str">
-        <v>Verifica que la expresión [N12] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N12] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="17">
@@ -2390,7 +2428,7 @@
         <v>N13</v>
       </c>
       <c r="E17" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F17" t="str">
         <v>0</v>
@@ -2399,7 +2437,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H17" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N13. La expresión indica que [N13] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N13 | La expresión indica que [N13] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I17" t="str">
         <v>-</v>
@@ -2411,7 +2449,7 @@
         <v>-</v>
       </c>
       <c r="L17" t="str">
-        <v>Verifica que la expresión [N13] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N13] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="18">
@@ -2428,7 +2466,7 @@
         <v>N14</v>
       </c>
       <c r="E18" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F18" t="str">
         <v>0</v>
@@ -2437,7 +2475,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H18" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N14. La expresión indica que [N14] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N14 | La expresión indica que [N14] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I18" t="str">
         <v>-</v>
@@ -2449,7 +2487,7 @@
         <v>-</v>
       </c>
       <c r="L18" t="str">
-        <v>Verifica que la expresión [N14] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N14] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="19">
@@ -2466,7 +2504,7 @@
         <v>N15</v>
       </c>
       <c r="E19" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F19" t="str">
         <v>0</v>
@@ -2475,7 +2513,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H19" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N15. La expresión indica que [N15] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N15 | La expresión indica que [N15] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I19" t="str">
         <v>-</v>
@@ -2487,7 +2525,7 @@
         <v>-</v>
       </c>
       <c r="L19" t="str">
-        <v>Verifica que la expresión [N15] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N15] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="20">
@@ -2504,7 +2542,7 @@
         <v>N16</v>
       </c>
       <c r="E20" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F20" t="str">
         <v>0</v>
@@ -2513,7 +2551,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H20" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N16. La expresión indica que [N16] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N16 | La expresión indica que [N16] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I20" t="str">
         <v>-</v>
@@ -2525,7 +2563,7 @@
         <v>-</v>
       </c>
       <c r="L20" t="str">
-        <v>Verifica que la expresión [N16] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N16] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="21">
@@ -2542,7 +2580,7 @@
         <v>O31</v>
       </c>
       <c r="E21" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F21" t="str">
         <v>0</v>
@@ -2551,7 +2589,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H21" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | O31. La expresión indica que [O31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | O31 | La expresión indica que [O31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
@@ -2563,7 +2601,7 @@
         <v>-</v>
       </c>
       <c r="L21" t="str">
-        <v>Verifica que la expresión [O31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [O31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="22">
@@ -2580,7 +2618,7 @@
         <v>O32</v>
       </c>
       <c r="E22" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F22" t="str">
         <v>0</v>
@@ -2589,7 +2627,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H22" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | O32. La expresión indica que [O32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | O32 | La expresión indica que [O32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
@@ -2601,7 +2639,7 @@
         <v>-</v>
       </c>
       <c r="L22" t="str">
-        <v>Verifica que la expresión [O32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [O32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="23">
@@ -2618,7 +2656,7 @@
         <v>P31</v>
       </c>
       <c r="E23" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F23" t="str">
         <v>0</v>
@@ -2627,7 +2665,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H23" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | P31. La expresión indica que [P31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | P31 | La expresión indica que [P31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
@@ -2639,7 +2677,7 @@
         <v>-</v>
       </c>
       <c r="L23" t="str">
-        <v>Verifica que la expresión [P31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [P31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="24">
@@ -2656,7 +2694,7 @@
         <v>P32</v>
       </c>
       <c r="E24" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F24" t="str">
         <v>0</v>
@@ -2665,7 +2703,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H24" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | P32. La expresión indica que [P32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | P32 | La expresión indica que [P32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
@@ -2677,7 +2715,7 @@
         <v>-</v>
       </c>
       <c r="L24" t="str">
-        <v>Verifica que la expresión [P32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [P32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="25">
@@ -2694,7 +2732,7 @@
         <v>Q31</v>
       </c>
       <c r="E25" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F25" t="str">
         <v>0</v>
@@ -2703,7 +2741,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H25" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Q31. La expresión indica que [Q31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Q31 | La expresión indica que [Q31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I25" t="str">
         <v>-</v>
@@ -2715,7 +2753,7 @@
         <v>-</v>
       </c>
       <c r="L25" t="str">
-        <v>Verifica que la expresión [Q31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [Q31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="26">
@@ -2732,7 +2770,7 @@
         <v>Q32</v>
       </c>
       <c r="E26" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F26" t="str">
         <v>0</v>
@@ -2741,7 +2779,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H26" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Q32. La expresión indica que [Q32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Q32 | La expresión indica que [Q32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
@@ -2753,7 +2791,7 @@
         <v>-</v>
       </c>
       <c r="L26" t="str">
-        <v>Verifica que la expresión [Q32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [Q32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="27">
@@ -2770,7 +2808,7 @@
         <v>R31</v>
       </c>
       <c r="E27" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F27" t="str">
         <v>0</v>
@@ -2779,7 +2817,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H27" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | R31. La expresión indica que [R31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | R31 | La expresión indica que [R31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
@@ -2791,7 +2829,7 @@
         <v>-</v>
       </c>
       <c r="L27" t="str">
-        <v>Verifica que la expresión [R31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [R31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="28">
@@ -2808,7 +2846,7 @@
         <v>R32</v>
       </c>
       <c r="E28" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F28" t="str">
         <v>0</v>
@@ -2817,7 +2855,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H28" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | R32. La expresión indica que [R32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | R32 | La expresión indica que [R32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
@@ -2829,7 +2867,7 @@
         <v>-</v>
       </c>
       <c r="L28" t="str">
-        <v>Verifica que la expresión [R32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [R32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="29">
@@ -2846,7 +2884,7 @@
         <v>S31</v>
       </c>
       <c r="E29" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F29" t="str">
         <v>0</v>
@@ -2855,7 +2893,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H29" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | S31. La expresión indica que [S31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | S31 | La expresión indica que [S31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
@@ -2867,7 +2905,7 @@
         <v>-</v>
       </c>
       <c r="L29" t="str">
-        <v>Verifica que la expresión [S31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [S31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="30">
@@ -2884,7 +2922,7 @@
         <v>S32</v>
       </c>
       <c r="E30" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F30" t="str">
         <v>0</v>
@@ -2893,7 +2931,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H30" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | S32. La expresión indica que [S32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | S32 | La expresión indica que [S32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I30" t="str">
         <v>-</v>
@@ -2905,7 +2943,7 @@
         <v>-</v>
       </c>
       <c r="L30" t="str">
-        <v>Verifica que la expresión [S32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [S32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="31">
@@ -2922,7 +2960,7 @@
         <v>T31</v>
       </c>
       <c r="E31" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F31" t="str">
         <v>0</v>
@@ -2931,7 +2969,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H31" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | T31. La expresión indica que [T31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | T31 | La expresión indica que [T31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I31" t="str">
         <v>-</v>
@@ -2943,7 +2981,7 @@
         <v>-</v>
       </c>
       <c r="L31" t="str">
-        <v>Verifica que la expresión [T31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [T31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="32">
@@ -2960,7 +2998,7 @@
         <v>T32</v>
       </c>
       <c r="E32" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F32" t="str">
         <v>0</v>
@@ -2969,7 +3007,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H32" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | T32. La expresión indica que [T32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | T32 | La expresión indica que [T32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I32" t="str">
         <v>-</v>
@@ -2981,7 +3019,7 @@
         <v>-</v>
       </c>
       <c r="L32" t="str">
-        <v>Verifica que la expresión [T32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [T32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="33">
@@ -2995,19 +3033,19 @@
         <v>CELDA</v>
       </c>
       <c r="D33" t="str">
-        <v>A05!C89</v>
+        <v>SUM(C19:C26, F36:F38)</v>
       </c>
       <c r="E33" t="str">
         <v>==</v>
       </c>
       <c r="F33" t="str">
-        <v>SUM(C19:C26, F36:F38)</v>
+        <v>A05!C89</v>
       </c>
       <c r="G33" t="str">
         <v>ERROR</v>
       </c>
       <c r="H33" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | A05, C89, C19, C26, F36, F38. La expresión indica que [A05!C89] debe ser igual a [SUM(C19:C26, F36:F38)].</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | C19, C26, F36, F38 | REM A05 | SECCIÓN E:  INGRESOS  A CONTROL DE SALUD DE RECIÉN NACIDOS | C89. La expresión indica que [SUM(C19:C26, F36:F38)] debe ser igual a [A05!C89].</v>
       </c>
       <c r="I33" t="str">
         <v>-</v>
@@ -3019,7 +3057,7 @@
         <v>-</v>
       </c>
       <c r="L33" t="str">
-        <v>Compara [A05!C89] sea igual a la suma del rango [SUM(C19:C26, F36:F38)].</v>
+        <v>Comparación cross-sheet: verifica que [SUM(C19:C26, F36:F38)] sea igual a [A05!C89] (referencia a otra hoja del libro).</v>
       </c>
     </row>
     <row r="34">
@@ -3045,7 +3083,7 @@
         <v>ERROR</v>
       </c>
       <c r="H34" t="str">
-        <v>REM A01 | SECCIÓN D: CONTROL DE SALUD INTEGRAL DE ADOLESCENTES (incluidos en sección B) | C74, T36, T38. La expresión indica que [C74] debe ser menor o igual a [T36:T38].</v>
+        <v>REM A01 | SECCIÓN D: CONTROL DE SALUD INTEGRAL DE ADOLESCENTES (incluidos en sección B) | C74 | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | T36, T38. La expresión indica que [C74] debe ser menor o igual a [T36:T38].</v>
       </c>
       <c r="I34" t="str">
         <v>-</v>
@@ -3083,7 +3121,7 @@
         <v>ERROR</v>
       </c>
       <c r="H35" t="str">
-        <v>REM A01 | SECCIÓN D: CONTROL DE SALUD INTEGRAL DE ADOLESCENTES (incluidos en sección B) | F74, U36, U38. La expresión indica que [F74] debe ser menor o igual a [U36:U38].</v>
+        <v>REM A01 | SECCIÓN D: CONTROL DE SALUD INTEGRAL DE ADOLESCENTES (incluidos en sección B) | F74 | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | U36, U38. La expresión indica que [F74] debe ser menor o igual a [U36:U38].</v>
       </c>
       <c r="I35" t="str">
         <v>-</v>
@@ -3112,7 +3150,7 @@
         <v>F36</v>
       </c>
       <c r="E36" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F36" t="str">
         <v>0</v>
@@ -3121,7 +3159,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H36" t="str">
-        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | F36. La expresión indica que [F36] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | F36 | La expresión indica que [F36] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I36" t="str">
         <v>-</v>
@@ -3133,7 +3171,7 @@
         <v>-</v>
       </c>
       <c r="L36" t="str">
-        <v>Verifica que la expresión [F36] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [F36] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="37">
@@ -3159,7 +3197,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H37" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | A03, L20, M20, O36, O37. La expresión indica que [A03!L20 + A03!M20] debe ser igual a [O36:O37].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | L20, M20 | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | O36, O37. La expresión indica que [A03!L20 + A03!M20] debe ser igual a [O36:O37].</v>
       </c>
       <c r="I37" t="str">
         <v>-</v>
@@ -3197,7 +3235,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H38" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | A03, N20, O20, A01, P36, P37. La expresión indica que [A03!N20 + A03!O20] debe ser igual a [A01!P36 + A01!P37].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | N20, O20 | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | P36, P37. La expresión indica que [A03!N20 + A03!O20] debe ser igual a [A01!P36 + A01!P37].</v>
       </c>
       <c r="I38" t="str">
         <v>-</v>
@@ -3235,7 +3273,7 @@
         <v>ERROR</v>
       </c>
       <c r="H39" t="str">
-        <v>REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | B11, B21. La expresión indica que [B11] debe ser igual a [B21].</v>
+        <v>REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | B11 | REM A02 | SECCIÓN B: EMP SEGÚN RESULTADO DEL ESTADO NUTRICIONAL | B21. La expresión indica que [B11] debe ser igual a [B21].</v>
       </c>
       <c r="I39" t="str">
         <v>-</v>
@@ -3273,7 +3311,7 @@
         <v>ERROR</v>
       </c>
       <c r="H40" t="str">
-        <v>REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | C11, C21. La expresión indica que [C11] debe ser igual a [C21].</v>
+        <v>REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | C11 | REM A02 | SECCIÓN B: EMP SEGÚN RESULTADO DEL ESTADO NUTRICIONAL | C21. La expresión indica que [C11] debe ser igual a [C21].</v>
       </c>
       <c r="I40" t="str">
         <v>-</v>
@@ -3311,7 +3349,7 @@
         <v>ERROR</v>
       </c>
       <c r="H41" t="str">
-        <v>REM A02 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A03, C108, C110, B11. La expresión indica que [A03!C108 + A03!C110] debe ser igual a [B11].</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C108, C110 | REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | B11. La expresión indica que [A03!C108 + A03!C110] debe ser igual a [B11].</v>
       </c>
       <c r="I41" t="str">
         <v>-</v>
@@ -3349,7 +3387,7 @@
         <v>ERROR</v>
       </c>
       <c r="H42" t="str">
-        <v>REM A02 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A03, C113, E11, F11. La expresión indica que [A03!C113] debe ser igual a [E11 + F11].</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C113 | REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | E11, F11. La expresión indica que [A03!C113] debe ser igual a [E11 + F11].</v>
       </c>
       <c r="I42" t="str">
         <v>-</v>
@@ -3387,7 +3425,7 @@
         <v>ERROR</v>
       </c>
       <c r="H43" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C20, C21, C36. La expresión indica que [C20] debe ser igual a [C21:C36].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C20 | REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C21, C36. La expresión indica que [C20] debe ser igual a [C21:C36].</v>
       </c>
       <c r="I43" t="str">
         <v>-</v>
@@ -3425,7 +3463,7 @@
         <v>ERROR</v>
       </c>
       <c r="H44" t="str">
-        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | C13, C14, C15. La expresión indica que [C13] debe ser igual a [C14:C15].</v>
+        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | C13 | REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | C14, C15. La expresión indica que [C13] debe ser igual a [C14:C15].</v>
       </c>
       <c r="I44" t="str">
         <v>-</v>
@@ -3463,7 +3501,7 @@
         <v>ERROR</v>
       </c>
       <c r="H45" t="str">
-        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | C54, C55, C57. La expresión indica que [C54] debe ser igual a [C55:C57].</v>
+        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | C54 | REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | C55, C57. La expresión indica que [C54] debe ser igual a [C55:C57].</v>
       </c>
       <c r="I45" t="str">
         <v>-</v>
@@ -3501,7 +3539,7 @@
         <v>ERROR</v>
       </c>
       <c r="H46" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C22, B46. La expresión indica que [C22] debe ser igual a [B46].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C22 | REM A03 | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | B46. La expresión indica que [C22] debe ser igual a [B46].</v>
       </c>
       <c r="I46" t="str">
         <v>-</v>
@@ -3539,7 +3577,7 @@
         <v>ERROR</v>
       </c>
       <c r="H47" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C23, B47. La expresión indica que [C23] debe ser igual a [B47].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C23 | REM A03 | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | B47. La expresión indica que [C23] debe ser igual a [B47].</v>
       </c>
       <c r="I47" t="str">
         <v>-</v>
@@ -3577,7 +3615,7 @@
         <v>ERROR</v>
       </c>
       <c r="H48" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C24, B48. La expresión indica que [C24] debe ser igual a [B48].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C24 | REM A03 | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | B48. La expresión indica que [C24] debe ser igual a [B48].</v>
       </c>
       <c r="I48" t="str">
         <v>-</v>
@@ -3615,7 +3653,7 @@
         <v>ERROR</v>
       </c>
       <c r="H49" t="str">
-        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | B86, A05, C11. La expresión indica que [B86] debe ser igual a [A05!C11].</v>
+        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | B86 | REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | C11. La expresión indica que [B86] debe ser igual a [A05!C11].</v>
       </c>
       <c r="I49" t="str">
         <v>-</v>
@@ -3653,7 +3691,7 @@
         <v>ERROR</v>
       </c>
       <c r="H50" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | C92, A01, H36, H37. La expresión indica que [C92] debe ser menor o igual a [A01!(H36:H37)].</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | C92 | REM A03 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A01, H36, H37. La expresión indica que [C92] debe ser menor o igual a [A01!(H36:H37)].</v>
       </c>
       <c r="I50" t="str">
         <v>-</v>
@@ -3691,7 +3729,7 @@
         <v>ERROR</v>
       </c>
       <c r="H51" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | C93, A01, L36, L37. La expresión indica que [C93] debe ser menor o igual a [A01!(L36:L37)].</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | C93 | REM A03 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A01, L36, L37. La expresión indica que [C93] debe ser menor o igual a [A01!(L36:L37)].</v>
       </c>
       <c r="I51" t="str">
         <v>-</v>
@@ -3729,7 +3767,7 @@
         <v>ERROR</v>
       </c>
       <c r="H52" t="str">
-        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | C97, A01, T36, U38. La expresión indica que [C97] debe ser igual a [A01!(T36:U38)].</v>
+        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | C97 | REM A03 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A01, T36, U38. La expresión indica que [C97] debe ser igual a [A01!(T36:U38)].</v>
       </c>
       <c r="I52" t="str">
         <v>-</v>
@@ -3767,7 +3805,7 @@
         <v>ERROR</v>
       </c>
       <c r="H53" t="str">
-        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C108, C114, C115, C117. La expresión indica que [C108:C114] debe ser igual a [C115:C117].</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C108, C114 | REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C115, C117. La expresión indica que [C108:C114] debe ser igual a [C115:C117].</v>
       </c>
       <c r="I53" t="str">
         <v>-</v>
@@ -3805,7 +3843,7 @@
         <v>ERROR</v>
       </c>
       <c r="H54" t="str">
-        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | C213, C214, C215. La expresión indica que [C213] debe ser igual a [C214+C215].</v>
+        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | C213 | REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | C214, C215. La expresión indica que [C213] debe ser igual a [C214+C215].</v>
       </c>
       <c r="I54" t="str">
         <v>-</v>
@@ -3843,7 +3881,7 @@
         <v>ERROR</v>
       </c>
       <c r="H55" t="str">
-        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | C61, C66, C67. La expresión indica que [C61:C66] debe ser igual a [C67].</v>
+        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | C61, C66 | REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | C67. La expresión indica que [C61:C66] debe ser igual a [C67].</v>
       </c>
       <c r="I55" t="str">
         <v>-</v>
@@ -3881,7 +3919,7 @@
         <v>ERROR</v>
       </c>
       <c r="H56" t="str">
-        <v>REM A04 | SECCIÓN B: CONSULTAS DE PROFESIONALES NO MÉDICOS | B39, B41, B135, B137. La expresión indica que [B39:B41] debe ser igual a [B135:B137].</v>
+        <v>REM A04 | SECCIÓN B: CONSULTAS DE PROFESIONALES NO MÉDICOS | B39, B41 | REM A04 | SECCIÓN K CLASIFICACIÓN DE CONSULTA NUTRICIONAL POR GRUPO DE EDAD (Incluidas en sección B) | B135, B137. La expresión indica que [B39:B41] debe ser igual a [B135:B137].</v>
       </c>
       <c r="I56" t="str">
         <v>-</v>
@@ -3919,7 +3957,7 @@
         <v>ERROR</v>
       </c>
       <c r="H57" t="str">
-        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | C141, C143, C146, C149. La expresión indica que [C141:C143] debe ser igual a [C146:C149].</v>
+        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | C141, C143 | REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | C146, C149. La expresión indica que [C141:C143] debe ser igual a [C146:C149].</v>
       </c>
       <c r="I57" t="str">
         <v>-</v>
@@ -3957,7 +3995,7 @@
         <v>ERROR</v>
       </c>
       <c r="H58" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C114, D114, E114, F114. La expresión indica que [C114+D114] debe ser igual a [E114+F114].</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C114, D114 | REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | E114, F114. La expresión indica que [C114+D114] debe ser igual a [E114+F114].</v>
       </c>
       <c r="I58" t="str">
         <v>-</v>
@@ -3995,7 +4033,7 @@
         <v>ERROR</v>
       </c>
       <c r="H59" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C115, D115, E115, F115. La expresión indica que [C115+D115] debe ser igual a [E115+F115].</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C115, D115 | REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | E115, F115. La expresión indica que [C115+D115] debe ser igual a [E115+F115].</v>
       </c>
       <c r="I59" t="str">
         <v>-</v>
@@ -4033,7 +4071,7 @@
         <v>ERROR</v>
       </c>
       <c r="H60" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C116, D116, E116, F116. La expresión indica que [C116+D116] debe ser igual a [E116+F116].</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C116, D116 | REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | E116, F116. La expresión indica que [C116+D116] debe ser igual a [E116+F116].</v>
       </c>
       <c r="I60" t="str">
         <v>-</v>
@@ -4071,7 +4109,7 @@
         <v>ERROR</v>
       </c>
       <c r="H61" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | M114, L114. La expresión indica que [M114] debe ser mayor o igual a [L114].</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | M114 | REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | L114. La expresión indica que [M114] debe ser mayor o igual a [L114].</v>
       </c>
       <c r="I61" t="str">
         <v>-</v>
@@ -4100,7 +4138,7 @@
         <v>L11:N14</v>
       </c>
       <c r="E62" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F62" t="str">
         <v>0</v>
@@ -4109,7 +4147,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H62" t="str">
-        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | L11, N14. La expresión indica que [L11:N14] la celda no debe contener datos.</v>
+        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | L11, N14 | La expresión indica que [L11:N14] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I62" t="str">
         <v>-</v>
@@ -4121,7 +4159,7 @@
         <v>-</v>
       </c>
       <c r="L62" t="str">
-        <v>Verifica que la expresión [L11:N14] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [L11:N14] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="63">
@@ -4147,7 +4185,7 @@
         <v>ERROR</v>
       </c>
       <c r="H63" t="str">
-        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | C119, C120, C127. La expresión indica que [C119] debe ser menor o igual a [C120:C127].</v>
+        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | C119 | REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | C120, C127. La expresión indica que [C119] debe ser menor o igual a [C120:C127].</v>
       </c>
       <c r="I63" t="str">
         <v>-</v>
@@ -4185,7 +4223,7 @@
         <v>ERROR</v>
       </c>
       <c r="H64" t="str">
-        <v>REM A05 | SECCIÓN J: INGRESOS Y EGRESOS AL PROGRAMA DE PACIENTES CON DEPENDENCIA LEVE, MODERADA Y SEVERA | AF146, AM150, C162. La expresión indica que [AF146:AM150] debe ser estrictamente mayor a [C162].</v>
+        <v>REM A05 | SECCIÓN J: INGRESOS Y EGRESOS AL PROGRAMA DE PACIENTES CON DEPENDENCIA LEVE, MODERADA Y SEVERA | AF146, AM150 | REM A05 | SECCIÓN K: INGRESOS AL PROGRAMA DEL ADULTO MAYOR SEGÚN CONDICIÓN DE FUNCIONALIDAD Y DEPENDENCIA | C162. La expresión indica que [AF146:AM150] debe ser estrictamente mayor a [C162].</v>
       </c>
       <c r="I64" t="str">
         <v>-</v>
@@ -4223,7 +4261,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H65" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C193, C204. La expresión indica que [C193] debe ser igual a [C204].</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C193 | REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C204. La expresión indica que [C193] debe ser igual a [C204].</v>
       </c>
       <c r="I65" t="str">
         <v>-</v>
@@ -4261,7 +4299,7 @@
         <v>ERROR</v>
       </c>
       <c r="H66" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C204, C205, C241. La expresión indica que [C204] debe ser menor o igual a [C205:C241].</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C204 | REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C205, C241. La expresión indica que [C204] debe ser menor o igual a [C205:C241].</v>
       </c>
       <c r="I66" t="str">
         <v>-</v>
@@ -4290,7 +4328,7 @@
         <v>C61:AL66</v>
       </c>
       <c r="E67" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F67" t="str">
         <v>0</v>
@@ -4299,7 +4337,7 @@
         <v>ERROR</v>
       </c>
       <c r="H67" t="str">
-        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | C61, AL66. La expresión indica que [C61:AL66] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | C61, AL66 | La expresión indica que [C61:AL66] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I67" t="str">
         <v>Tipo: HOSPITAL, SAPU, SUR</v>
@@ -4311,7 +4349,7 @@
         <v>-</v>
       </c>
       <c r="L67" t="str">
-        <v>Verifica que la expresión [C61:AL66] NO contenga datos (sea cero o vacía). | Solo aplica a tipo: HOSPITAL, SAPU, SUR. Excluye códigos: 123000, 123100, 123101, 123102, 123103, 123104, 123105, 123800, 123801, 200085, 200747, 200748, 200749, 200750</v>
+        <v>Verifica que la expresión [C61:AL66] contenga datos (no sea cero ni vacía). | Solo aplica a tipo: HOSPITAL, SAPU, SUR. Excluye códigos: 123000, 123100, 123101, 123102, 123103, 123104, 123105, 123800, 123801, 200085, 200747, 200748, 200749, 200750</v>
       </c>
     </row>
     <row r="68">
@@ -4337,7 +4375,7 @@
         <v>ERROR</v>
       </c>
       <c r="H68" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | B13, B14, B78. La expresión indica que [B13+B14] debe ser igual a [B78].</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | B13, B14 | REM A08 | SECCIÓN B.1: CATEGORIZACIÓN DE PACIENTES DE URGENCIA GINECO OBSTÉTRICA PREVIO A LA ATENCIÓN CLÍNICA POR MATRÓN (A) Y/O MÉDICO GINECO-OBSTETRA (Establecimientos alta, mediana y baja complejidad) | B78. La expresión indica que [B13+B14] debe ser igual a [B78].</v>
       </c>
       <c r="I68" t="str">
         <v>-</v>
@@ -4366,7 +4404,7 @@
         <v>C171:F171</v>
       </c>
       <c r="E69" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F69" t="str">
         <v>0</v>
@@ -4375,7 +4413,7 @@
         <v>ERROR</v>
       </c>
       <c r="H69" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | C171, F171. La expresión indica que [C171:F171] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | C171, F171 | La expresión indica que [C171:F171] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I69" t="str">
         <v>-</v>
@@ -4387,7 +4425,7 @@
         <v>-</v>
       </c>
       <c r="L69" t="str">
-        <v>Verifica que la expresión [C171:F171] NO contenga datos (sea cero o vacía). | Excluye códigos: 123000, 123102, 123101, 123104, 123105, 123311, 200747, 200748, 200749, 200750</v>
+        <v>Verifica que la expresión [C171:F171] contenga datos (no sea cero ni vacía). | Excluye códigos: 123000, 123102, 123101, 123104, 123105, 123311, 200747, 200748, 200749, 200750</v>
       </c>
     </row>
     <row r="70">
@@ -4404,7 +4442,7 @@
         <v>C172:F174</v>
       </c>
       <c r="E70" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F70" t="str">
         <v>0</v>
@@ -4413,7 +4451,7 @@
         <v>ERROR</v>
       </c>
       <c r="H70" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | C172, F174. La expresión indica que [C172:F174] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | C172, F174 | La expresión indica que [C172:F174] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I70" t="str">
         <v>-</v>
@@ -4425,7 +4463,7 @@
         <v>-</v>
       </c>
       <c r="L70" t="str">
-        <v>Verifica que la expresión [C172:F174] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [C172:F174] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="71">
@@ -4442,7 +4480,7 @@
         <v>E178:E183</v>
       </c>
       <c r="E71" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F71" t="str">
         <v>0</v>
@@ -4451,7 +4489,7 @@
         <v>ERROR</v>
       </c>
       <c r="H71" t="str">
-        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | E178, E183. La expresión indica que [E178:E183] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | E178, E183 | La expresión indica que [E178:E183] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I71" t="str">
         <v>-</v>
@@ -4463,7 +4501,7 @@
         <v>-</v>
       </c>
       <c r="L71" t="str">
-        <v>Verifica que la expresión [E178:E183] NO contenga datos (sea cero o vacía). | Excluye tipo: SAMU. Excluye códigos: 123010</v>
+        <v>Verifica que la expresión [E178:E183] contenga datos (no sea cero ni vacía). | Excluye tipo: SAMU. Excluye códigos: 123010</v>
       </c>
     </row>
     <row r="72">
@@ -4480,7 +4518,7 @@
         <v>C161+D161</v>
       </c>
       <c r="E72" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F72" t="str">
         <v>0</v>
@@ -4489,7 +4527,7 @@
         <v>ERROR</v>
       </c>
       <c r="H72" t="str">
-        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | C161, D161. La expresión indica que [C161+D161] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | C161, D161 | La expresión indica que [C161+D161] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I72" t="str">
         <v>-</v>
@@ -4501,7 +4539,7 @@
         <v>-</v>
       </c>
       <c r="L72" t="str">
-        <v>Verifica que la expresión [C161+D161] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [C161+D161] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="73">
@@ -4527,7 +4565,7 @@
         <v>ERROR</v>
       </c>
       <c r="H73" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | B13, AS13. La expresión indica que [B13] debe ser estrictamente menor a [AS13].</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | B13 | REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | AS13. La expresión indica que [B13] debe ser estrictamente menor a [AS13].</v>
       </c>
       <c r="I73" t="str">
         <v>-</v>
@@ -4544,31 +4582,31 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>A19b-VAL001</v>
+        <v>A09-VAL001</v>
       </c>
       <c r="B74" t="str">
-        <v>A19b</v>
+        <v>A09</v>
       </c>
       <c r="C74" t="str">
         <v>CELDA</v>
       </c>
       <c r="D74" t="str">
-        <v>B11</v>
+        <v>D16+D17</v>
       </c>
       <c r="E74" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F74" t="str">
-        <v>E11:I11</v>
+        <v>0</v>
       </c>
       <c r="G74" t="str">
         <v>REVISAR</v>
       </c>
       <c r="H74" t="str">
-        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | B11, E11, I11. La expresión indica que [B11] debe ser igual a [E11:I11].</v>
+        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | D16, D17 | La expresión indica que [D16+D17] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I74" t="str">
-        <v>-</v>
+        <v>Códigos: 123000, 123100, 123101, 123102</v>
       </c>
       <c r="J74" t="str">
         <v>-</v>
@@ -4577,185 +4615,185 @@
         <v>-</v>
       </c>
       <c r="L74" t="str">
-        <v>Compara [B11] sea igual a la suma del rango [E11:I11].</v>
+        <v>Verifica que la expresión [D16+D17] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123000, 123100, 123101, 123102</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>A27-VAL001</v>
+        <v>A11-VAL001</v>
       </c>
       <c r="B75" t="str">
-        <v>A27</v>
+        <v>A11</v>
       </c>
       <c r="C75" t="str">
         <v>CELDA</v>
       </c>
       <c r="D75" t="str">
-        <v>D53</v>
+        <v>B13:C30</v>
       </c>
       <c r="E75" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F75" t="str">
-        <v>D98</v>
+        <v>0</v>
       </c>
       <c r="G75" t="str">
-        <v>REVISAR</v>
+        <v>ERROR</v>
       </c>
       <c r="H75" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | D53. La expresión indica que [D53] debe ser igual a [D98].</v>
+        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | B13, C30 | La expresión indica que [B13:C30] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I75" t="str">
-        <v>-</v>
+        <v>Códigos: 123000, 123100</v>
       </c>
       <c r="J75" t="str">
         <v>-</v>
       </c>
       <c r="K75" t="str">
-        <v>Omitir si exp1=0</v>
+        <v>-</v>
       </c>
       <c r="L75" t="str">
-        <v>Compara [D53] sea igual a [D98]. | Se omite si expresión_1 es 0</v>
+        <v>Verifica que la expresión [B13:C30] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123000, 123100</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>A27-VAL002</v>
+        <v>A11-VAL002</v>
       </c>
       <c r="B76" t="str">
-        <v>A27</v>
+        <v>A11</v>
       </c>
       <c r="C76" t="str">
         <v>CELDA</v>
       </c>
       <c r="D76" t="str">
-        <v>D23</v>
+        <v>C144:P148</v>
       </c>
       <c r="E76" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F76" t="str">
-        <v>Y23:AA23</v>
+        <v>0</v>
       </c>
       <c r="G76" t="str">
-        <v>REVISAR</v>
+        <v>ERROR</v>
       </c>
       <c r="H76" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | D23. La expresión indica que [D23] debe ser igual a [Y23:AA23].</v>
+        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | C144, P148 | La expresión indica que [C144:P148] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I76" t="str">
-        <v>-</v>
+        <v>Códigos: 123000, 123100</v>
       </c>
       <c r="J76" t="str">
         <v>-</v>
       </c>
       <c r="K76" t="str">
-        <v>Omitir si exp1=0</v>
+        <v>-</v>
       </c>
       <c r="L76" t="str">
-        <v>Compara [D23] sea igual a la suma del rango [Y23:AA23]. | Se omite si expresión_1 es 0</v>
+        <v>Verifica que la expresión [C144:P148] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123000, 123100</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>A28-VAL001</v>
+        <v>A11-VAL003</v>
       </c>
       <c r="B77" t="str">
-        <v>A28</v>
+        <v>A11</v>
       </c>
       <c r="C77" t="str">
         <v>CELDA</v>
       </c>
       <c r="D77" t="str">
-        <v>B13</v>
+        <v>C152:P156</v>
       </c>
       <c r="E77" t="str">
-        <v>&lt;=</v>
+        <v>!=</v>
       </c>
       <c r="F77" t="str">
-        <v>B61</v>
+        <v>0</v>
       </c>
       <c r="G77" t="str">
         <v>ERROR</v>
       </c>
       <c r="H77" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13, B61. La expresión indica que [B13] debe ser menor o igual a [B61].</v>
+        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | C152, P156 | La expresión indica que [C152:P156] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I77" t="str">
-        <v>-</v>
+        <v>Códigos: 123000, 123100</v>
       </c>
       <c r="J77" t="str">
         <v>-</v>
       </c>
       <c r="K77" t="str">
-        <v>Omitir si ambos=0</v>
+        <v>Omitir si exp1=0</v>
       </c>
       <c r="L77" t="str">
-        <v>Compara [B13] sea menor o igual a [B61]. | Se omite si ambas expresiones son 0</v>
+        <v>Verifica que la expresión [C152:P156] contenga datos (no sea cero ni vacía). | Se omite si expresión_1 es 0. Solo aplica a códigos: 123000, 123100</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>A28-VAL002</v>
+        <v>A11-VAL004</v>
       </c>
       <c r="B78" t="str">
-        <v>A28</v>
+        <v>A11</v>
       </c>
       <c r="C78" t="str">
         <v>CELDA</v>
       </c>
       <c r="D78" t="str">
-        <v>B13</v>
+        <v>C161:D183</v>
       </c>
       <c r="E78" t="str">
-        <v>&gt;=</v>
+        <v>!=</v>
       </c>
       <c r="F78" t="str">
-        <v>B14</v>
+        <v>0</v>
       </c>
       <c r="G78" t="str">
         <v>ERROR</v>
       </c>
       <c r="H78" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13, B14. La expresión indica que [B13] debe ser mayor o igual a [B14].</v>
+        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | C161, D183 | La expresión indica que [C161:D183] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I78" t="str">
-        <v>-</v>
+        <v>Códigos: 123000, 123100</v>
       </c>
       <c r="J78" t="str">
         <v>-</v>
       </c>
       <c r="K78" t="str">
-        <v>Omitir si ambos=0</v>
+        <v>-</v>
       </c>
       <c r="L78" t="str">
-        <v>Compara [B13] sea mayor o igual a [B14]. | Se omite si ambas expresiones son 0</v>
+        <v>Verifica que la expresión [C161:D183] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123000, 123100</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>A28-VAL003</v>
+        <v>A19a-VAL001</v>
       </c>
       <c r="B79" t="str">
-        <v>A28</v>
+        <v>A19a</v>
       </c>
       <c r="C79" t="str">
         <v>CELDA</v>
       </c>
       <c r="D79" t="str">
-        <v>B13</v>
+        <v>C129:C148</v>
       </c>
       <c r="E79" t="str">
-        <v>&gt;=</v>
+        <v>&lt;=</v>
       </c>
       <c r="F79" t="str">
-        <v>B15</v>
+        <v>O129:O148</v>
       </c>
       <c r="G79" t="str">
         <v>ERROR</v>
       </c>
       <c r="H79" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13, B15. La expresión indica que [B13] debe ser mayor o igual a [B15].</v>
+        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | C129, C148 | REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | O129, O148. La expresión indica que [C129:C148] debe ser menor o igual a [O129:O148].</v>
       </c>
       <c r="I79" t="str">
         <v>-</v>
@@ -4764,36 +4802,36 @@
         <v>-</v>
       </c>
       <c r="K79" t="str">
-        <v>Omitir si ambos=0</v>
+        <v>Omitir si exp1=0</v>
       </c>
       <c r="L79" t="str">
-        <v>Compara [B13] sea mayor o igual a [B15]. | Se omite si ambas expresiones son 0</v>
+        <v>Compara [C129:C148] sea menor o igual a la suma del rango [O129:O148]. | Se omite si expresión_1 es 0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>A28-VAL004</v>
+        <v>A19b-VAL001</v>
       </c>
       <c r="B80" t="str">
-        <v>A28</v>
+        <v>A19b</v>
       </c>
       <c r="C80" t="str">
         <v>CELDA</v>
       </c>
       <c r="D80" t="str">
-        <v>B29</v>
+        <v>B11</v>
       </c>
       <c r="E80" t="str">
-        <v>&lt;=</v>
+        <v>==</v>
       </c>
       <c r="F80" t="str">
-        <v>B30:B52</v>
+        <v>E11:I11</v>
       </c>
       <c r="G80" t="str">
-        <v>ERROR</v>
+        <v>REVISAR</v>
       </c>
       <c r="H80" t="str">
-        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | B29, B30, B52. La expresión indica que [B29] debe ser menor o igual a [B30:B52].</v>
+        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | B11 | REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | E11, I11. La expresión indica que [B11] debe ser igual a [E11:I11].</v>
       </c>
       <c r="I80" t="str">
         <v>-</v>
@@ -4802,36 +4840,36 @@
         <v>-</v>
       </c>
       <c r="K80" t="str">
-        <v>Omitir si ambos=0</v>
+        <v>-</v>
       </c>
       <c r="L80" t="str">
-        <v>Compara [B29] sea menor o igual a la suma del rango [B30:B52]. | Se omite si ambas expresiones son 0</v>
+        <v>Compara [B11] sea igual a la suma del rango [E11:I11].</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>A28-VAL005</v>
+        <v>A27-VAL001</v>
       </c>
       <c r="B81" t="str">
-        <v>A28</v>
+        <v>A27</v>
       </c>
       <c r="C81" t="str">
         <v>CELDA</v>
       </c>
       <c r="D81" t="str">
-        <v>B149</v>
+        <v>D53</v>
       </c>
       <c r="E81" t="str">
-        <v>&lt;=</v>
+        <v>&gt;=</v>
       </c>
       <c r="F81" t="str">
-        <v>B150:B177</v>
+        <v>D98</v>
       </c>
       <c r="G81" t="str">
-        <v>ERROR</v>
+        <v>REVISAR</v>
       </c>
       <c r="H81" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | B149, B150, B177. La expresión indica que [B149] debe ser menor o igual a [B150:B177].</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | D53 | REM A27 | SECCIÓN B: ACTIVIDADES DE EDUCACIÓN PARA LA SALUD SEGÚN PERSONAL QUE LAS REALIZA (SESIONES) | D98. La expresión indica que [D53] debe ser mayor o igual a [D98].</v>
       </c>
       <c r="I81" t="str">
         <v>-</v>
@@ -4840,36 +4878,36 @@
         <v>-</v>
       </c>
       <c r="K81" t="str">
-        <v>Omitir si ambos=0</v>
+        <v>Omitir si exp1=0</v>
       </c>
       <c r="L81" t="str">
-        <v>Compara [B149] sea menor o igual a la suma del rango [B150:B177]. | Se omite si ambas expresiones son 0</v>
+        <v>Compara [D53] sea mayor o igual a [D98]. | Se omite si expresión_1 es 0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>A28-VAL006</v>
+        <v>A27-VAL002</v>
       </c>
       <c r="B82" t="str">
-        <v>A28</v>
+        <v>A27</v>
       </c>
       <c r="C82" t="str">
         <v>CELDA</v>
       </c>
       <c r="D82" t="str">
-        <v>AM150:AM178</v>
+        <v>D23</v>
       </c>
       <c r="E82" t="str">
-        <v>==</v>
+        <v>&gt;=</v>
       </c>
       <c r="F82" t="str">
-        <v>0</v>
+        <v>Y23:AA23</v>
       </c>
       <c r="G82" t="str">
         <v>REVISAR</v>
       </c>
       <c r="H82" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | AM150, AM178. La expresión indica que [AM150:AM178] la celda no debe contener datos.</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | D23 | REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Y23, AA23. La expresión indica que [D23] debe ser mayor o igual a [Y23:AA23].</v>
       </c>
       <c r="I82" t="str">
         <v>-</v>
@@ -4878,36 +4916,36 @@
         <v>-</v>
       </c>
       <c r="K82" t="str">
-        <v>-</v>
+        <v>Omitir si exp1=0</v>
       </c>
       <c r="L82" t="str">
-        <v>Verifica que la expresión [AM150:AM178] NO contenga datos (sea cero o vacía).</v>
+        <v>Compara [D23] sea mayor o igual a la suma del rango [Y23:AA23]. | Se omite si expresión_1 es 0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>A29-VAL001</v>
+        <v>A28-VAL001</v>
       </c>
       <c r="B83" t="str">
-        <v>A29</v>
+        <v>A28</v>
       </c>
       <c r="C83" t="str">
         <v>CELDA</v>
       </c>
       <c r="D83" t="str">
-        <v>O12:P12</v>
+        <v>B13</v>
       </c>
       <c r="E83" t="str">
-        <v>==</v>
+        <v>&lt;=</v>
       </c>
       <c r="F83" t="str">
-        <v>0</v>
+        <v>B61</v>
       </c>
       <c r="G83" t="str">
         <v>ERROR</v>
       </c>
       <c r="H83" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | O12, P12. La expresión indica que [O12:P12] la celda no debe contener datos.</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13 | REM A28 | SECCIÓN A.3: EVALUACIÓN INICIAL | B61. La expresión indica que [B13] debe ser menor o igual a [B61].</v>
       </c>
       <c r="I83" t="str">
         <v>-</v>
@@ -4916,36 +4954,36 @@
         <v>-</v>
       </c>
       <c r="K83" t="str">
-        <v>-</v>
+        <v>Omitir si ambos=0</v>
       </c>
       <c r="L83" t="str">
-        <v>Verifica que la expresión [O12:P12] NO contenga datos (sea cero o vacía).</v>
+        <v>Compara [B13] sea menor o igual a [B61]. | Se omite si ambas expresiones son 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>A29-VAL002</v>
+        <v>A28-VAL002</v>
       </c>
       <c r="B84" t="str">
-        <v>A29</v>
+        <v>A28</v>
       </c>
       <c r="C84" t="str">
         <v>CELDA</v>
       </c>
       <c r="D84" t="str">
-        <v>M13:N13</v>
+        <v>B13</v>
       </c>
       <c r="E84" t="str">
-        <v>==</v>
+        <v>&gt;=</v>
       </c>
       <c r="F84" t="str">
-        <v>0</v>
+        <v>B14</v>
       </c>
       <c r="G84" t="str">
         <v>ERROR</v>
       </c>
       <c r="H84" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | M13, N13. La expresión indica que [M13:N13] la celda no debe contener datos.</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13 | REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B14. La expresión indica que [B13] debe ser mayor o igual a [B14].</v>
       </c>
       <c r="I84" t="str">
         <v>-</v>
@@ -4954,36 +4992,36 @@
         <v>-</v>
       </c>
       <c r="K84" t="str">
-        <v>-</v>
+        <v>Omitir si ambos=0</v>
       </c>
       <c r="L84" t="str">
-        <v>Verifica que la expresión [M13:N13] NO contenga datos (sea cero o vacía).</v>
+        <v>Compara [B13] sea mayor o igual a [B14]. | Se omite si ambas expresiones son 0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>A30-VAL001</v>
+        <v>A28-VAL003</v>
       </c>
       <c r="B85" t="str">
-        <v>A30R</v>
+        <v>A28</v>
       </c>
       <c r="C85" t="str">
         <v>CELDA</v>
       </c>
       <c r="D85" t="str">
-        <v>B16:B17</v>
+        <v>B13</v>
       </c>
       <c r="E85" t="str">
-        <v>==</v>
+        <v>&gt;=</v>
       </c>
       <c r="F85" t="str">
-        <v>0</v>
+        <v>B15</v>
       </c>
       <c r="G85" t="str">
         <v>ERROR</v>
       </c>
       <c r="H85" t="str">
-        <v>REM A30R | Sección Desconocida | B16, B17. La expresión indica que [B16:B17] la celda no debe contener datos.</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B13 | REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | B15. La expresión indica que [B13] debe ser mayor o igual a [B15].</v>
       </c>
       <c r="I85" t="str">
         <v>-</v>
@@ -4992,115 +5030,115 @@
         <v>-</v>
       </c>
       <c r="K85" t="str">
-        <v>-</v>
+        <v>Omitir si ambos=0</v>
       </c>
       <c r="L85" t="str">
-        <v>Verifica que la expresión [B16:B17] NO contenga datos (sea cero o vacía).</v>
+        <v>Compara [B13] sea mayor o igual a [B15]. | Se omite si ambas expresiones son 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>A09-VAL001</v>
+        <v>A28-VAL004</v>
       </c>
       <c r="B86" t="str">
-        <v>A09</v>
+        <v>A28</v>
       </c>
       <c r="C86" t="str">
         <v>CELDA</v>
       </c>
       <c r="D86" t="str">
-        <v>D16+D17</v>
+        <v>B29</v>
       </c>
       <c r="E86" t="str">
-        <v>!=</v>
+        <v>&lt;=</v>
       </c>
       <c r="F86" t="str">
-        <v>0</v>
+        <v>B30:B52</v>
       </c>
       <c r="G86" t="str">
-        <v>REVISAR</v>
+        <v>ERROR</v>
       </c>
       <c r="H86" t="str">
-        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | D16, D17. La expresión indica que [D16+D17] la celda debe contener datos.</v>
+        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | B29 | REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | B30, B52. La expresión indica que [B29] debe ser menor o igual a [B30:B52].</v>
       </c>
       <c r="I86" t="str">
-        <v>Códigos: 123000, 123100, 123101, 123102</v>
+        <v>-</v>
       </c>
       <c r="J86" t="str">
         <v>-</v>
       </c>
       <c r="K86" t="str">
-        <v>-</v>
+        <v>Omitir si ambos=0</v>
       </c>
       <c r="L86" t="str">
-        <v>Verifica que la expresión [D16+D17] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123000, 123100, 123101, 123102</v>
+        <v>Compara [B29] sea menor o igual a la suma del rango [B30:B52]. | Se omite si ambas expresiones son 0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>A11-VAL001</v>
+        <v>A28-VAL005</v>
       </c>
       <c r="B87" t="str">
-        <v>A11</v>
+        <v>A28</v>
       </c>
       <c r="C87" t="str">
         <v>CELDA</v>
       </c>
       <c r="D87" t="str">
-        <v>B13:C30</v>
+        <v>B149</v>
       </c>
       <c r="E87" t="str">
-        <v>!=</v>
+        <v>&lt;=</v>
       </c>
       <c r="F87" t="str">
-        <v>0</v>
+        <v>B150:B177</v>
       </c>
       <c r="G87" t="str">
         <v>ERROR</v>
       </c>
       <c r="H87" t="str">
-        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | B13, C30. La expresión indica que [B13:C30] la celda debe contener datos.</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | B149 | REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | B150, B177. La expresión indica que [B149] debe ser menor o igual a [B150:B177].</v>
       </c>
       <c r="I87" t="str">
-        <v>Códigos: 123000, 123100</v>
+        <v>-</v>
       </c>
       <c r="J87" t="str">
         <v>-</v>
       </c>
       <c r="K87" t="str">
-        <v>-</v>
+        <v>Omitir si ambos=0</v>
       </c>
       <c r="L87" t="str">
-        <v>Verifica que la expresión [B13:C30] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123000, 123100</v>
+        <v>Compara [B149] sea menor o igual a la suma del rango [B150:B177]. | Se omite si ambas expresiones son 0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>A11-VAL002</v>
+        <v>A28-VAL006</v>
       </c>
       <c r="B88" t="str">
-        <v>A11</v>
+        <v>A28</v>
       </c>
       <c r="C88" t="str">
         <v>CELDA</v>
       </c>
       <c r="D88" t="str">
-        <v>C144:P148</v>
+        <v>AM149:AM177</v>
       </c>
       <c r="E88" t="str">
-        <v>!=</v>
+        <v>&gt;=</v>
       </c>
       <c r="F88" t="str">
         <v>0</v>
       </c>
       <c r="G88" t="str">
-        <v>ERROR</v>
+        <v>REVISAR</v>
       </c>
       <c r="H88" t="str">
-        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | C144, P148. La expresión indica que [C144:P148] la celda debe contener datos.</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | AM149, AM177 | La expresión indica que [AM149:AM177] debe ser mayor o igual a [0].</v>
       </c>
       <c r="I88" t="str">
-        <v>Códigos: 123000, 123100</v>
+        <v>Códigos: 123100, 123101, 123102</v>
       </c>
       <c r="J88" t="str">
         <v>-</v>
@@ -5109,21 +5147,21 @@
         <v>-</v>
       </c>
       <c r="L88" t="str">
-        <v>Verifica que la expresión [C144:P148] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123000, 123100</v>
+        <v>Compara [AM149:AM177] sea mayor o igual a 0. | Solo aplica a códigos: 123100, 123101, 123102</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>A11-VAL003</v>
+        <v>A28-VAL007</v>
       </c>
       <c r="B89" t="str">
-        <v>A11</v>
+        <v>A28</v>
       </c>
       <c r="C89" t="str">
         <v>CELDA</v>
       </c>
       <c r="D89" t="str">
-        <v>C152:P156</v>
+        <v>AM149:AM177</v>
       </c>
       <c r="E89" t="str">
         <v>!=</v>
@@ -5135,33 +5173,33 @@
         <v>ERROR</v>
       </c>
       <c r="H89" t="str">
-        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | C152, P156. La expresión indica que [C152:P156] la celda debe contener datos.</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | AM149, AM177 | La expresión indica que [AM149:AM177] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I89" t="str">
-        <v>Códigos: 123000, 123100</v>
+        <v>Códigos: 123100, 123101, 123102</v>
       </c>
       <c r="J89" t="str">
         <v>-</v>
       </c>
       <c r="K89" t="str">
-        <v>Omitir si exp1=0</v>
+        <v>-</v>
       </c>
       <c r="L89" t="str">
-        <v>Verifica que la expresión [C152:P156] contenga datos (no sea cero ni vacía). | Se omite si expresión_1 es 0. Solo aplica a códigos: 123000, 123100</v>
+        <v>Verifica que la expresión [AM149:AM177] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123100, 123101, 123102</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>A11-VAL004</v>
+        <v>A29-VAL001</v>
       </c>
       <c r="B90" t="str">
-        <v>A11</v>
+        <v>A29</v>
       </c>
       <c r="C90" t="str">
         <v>CELDA</v>
       </c>
       <c r="D90" t="str">
-        <v>C161:D183</v>
+        <v>O12:P12</v>
       </c>
       <c r="E90" t="str">
         <v>!=</v>
@@ -5173,10 +5211,10 @@
         <v>ERROR</v>
       </c>
       <c r="H90" t="str">
-        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | C161, D183. La expresión indica que [C161:D183] la celda debe contener datos.</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | O12, P12 | La expresión indica que [O12:P12] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I90" t="str">
-        <v>Códigos: 123000, 123100</v>
+        <v>-</v>
       </c>
       <c r="J90" t="str">
         <v>-</v>
@@ -5185,33 +5223,33 @@
         <v>-</v>
       </c>
       <c r="L90" t="str">
-        <v>Verifica que la expresión [C161:D183] contenga datos (no sea cero ni vacía). | Solo aplica a códigos: 123000, 123100</v>
+        <v>Verifica que la expresión [O12:P12] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>A19a-VAL001</v>
+        <v>A29-VAL002</v>
       </c>
       <c r="B91" t="str">
-        <v>A19a</v>
+        <v>A29</v>
       </c>
       <c r="C91" t="str">
         <v>CELDA</v>
       </c>
       <c r="D91" t="str">
-        <v>C129:C148</v>
+        <v>M13:N13</v>
       </c>
       <c r="E91" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F91" t="str">
-        <v>O129:O148</v>
+        <v>0</v>
       </c>
       <c r="G91" t="str">
         <v>ERROR</v>
       </c>
       <c r="H91" t="str">
-        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | C129, C148, O129, O148. La expresión indica que [C129:C148] debe ser igual a [O129:O148].</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | M13, N13 | La expresión indica que [M13:N13] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I91" t="str">
         <v>-</v>
@@ -5223,12 +5261,50 @@
         <v>-</v>
       </c>
       <c r="L91" t="str">
-        <v>Compara [C129:C148] sea igual a la suma del rango [O129:O148].</v>
+        <v>Verifica que la expresión [M13:N13] contenga datos (no sea cero ni vacía).</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>A30R-VAL001</v>
+      </c>
+      <c r="B92" t="str">
+        <v>A30R</v>
+      </c>
+      <c r="C92" t="str">
+        <v>CELDA</v>
+      </c>
+      <c r="D92" t="str">
+        <v>B16:B17</v>
+      </c>
+      <c r="E92" t="str">
+        <v>!=</v>
+      </c>
+      <c r="F92" t="str">
+        <v>0</v>
+      </c>
+      <c r="G92" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="H92" t="str">
+        <v>REM A30R | Sección Desconocida | B16, B17 | La expresión indica que [B16:B17] la celda debe contener datos (distinto de cero).</v>
+      </c>
+      <c r="I92" t="str">
+        <v>-</v>
+      </c>
+      <c r="J92" t="str">
+        <v>-</v>
+      </c>
+      <c r="K92" t="str">
+        <v>-</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Verifica que la expresión [B16:B17] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L92"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5708,7 +5784,7 @@
         <v>F11</v>
       </c>
       <c r="E2" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F2" t="str">
         <v>0</v>
@@ -5717,7 +5793,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | F11. La expresión indica que [F11] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | F11 | La expresión indica que [F11] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -5729,7 +5805,7 @@
         <v>-</v>
       </c>
       <c r="L2" t="str">
-        <v>Verifica que la expresión [F11] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [F11] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="3">
@@ -5746,7 +5822,7 @@
         <v>F12</v>
       </c>
       <c r="E3" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F3" t="str">
         <v>0</v>
@@ -5755,7 +5831,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | F12. La expresión indica que [F12] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | F12 | La expresión indica que [F12] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -5767,7 +5843,7 @@
         <v>-</v>
       </c>
       <c r="L3" t="str">
-        <v>Verifica que la expresión [F12] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [F12] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="4">
@@ -5784,7 +5860,7 @@
         <v>M11</v>
       </c>
       <c r="E4" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F4" t="str">
         <v>0</v>
@@ -5793,7 +5869,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H4" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | M11. La expresión indica que [M11] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | M11 | La expresión indica que [M11] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I4" t="str">
         <v>-</v>
@@ -5805,7 +5881,7 @@
         <v>-</v>
       </c>
       <c r="L4" t="str">
-        <v>Verifica que la expresión [M11] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [M11] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="5">
@@ -5822,7 +5898,7 @@
         <v>M12</v>
       </c>
       <c r="E5" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F5" t="str">
         <v>0</v>
@@ -5831,7 +5907,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H5" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | M12. La expresión indica que [M12] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | M12 | La expresión indica que [M12] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I5" t="str">
         <v>-</v>
@@ -5843,7 +5919,7 @@
         <v>-</v>
       </c>
       <c r="L5" t="str">
-        <v>Verifica que la expresión [M12] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [M12] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="6">
@@ -5860,7 +5936,7 @@
         <v>N11</v>
       </c>
       <c r="E6" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F6" t="str">
         <v>0</v>
@@ -5869,7 +5945,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H6" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N11. La expresión indica que [N11] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N11 | La expresión indica que [N11] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I6" t="str">
         <v>-</v>
@@ -5881,7 +5957,7 @@
         <v>-</v>
       </c>
       <c r="L6" t="str">
-        <v>Verifica que la expresión [N11] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N11] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="7">
@@ -5898,7 +5974,7 @@
         <v>N12</v>
       </c>
       <c r="E7" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F7" t="str">
         <v>0</v>
@@ -5907,7 +5983,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H7" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N12. La expresión indica que [N12] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N12 | La expresión indica que [N12] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I7" t="str">
         <v>-</v>
@@ -5919,7 +5995,7 @@
         <v>-</v>
       </c>
       <c r="L7" t="str">
-        <v>Verifica que la expresión [N12] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N12] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="8">
@@ -5936,7 +6012,7 @@
         <v>N13</v>
       </c>
       <c r="E8" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F8" t="str">
         <v>0</v>
@@ -5945,7 +6021,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H8" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N13. La expresión indica que [N13] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N13 | La expresión indica que [N13] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I8" t="str">
         <v>-</v>
@@ -5957,7 +6033,7 @@
         <v>-</v>
       </c>
       <c r="L8" t="str">
-        <v>Verifica que la expresión [N13] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N13] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="9">
@@ -5974,7 +6050,7 @@
         <v>N14</v>
       </c>
       <c r="E9" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F9" t="str">
         <v>0</v>
@@ -5983,7 +6059,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H9" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N14. La expresión indica que [N14] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N14 | La expresión indica que [N14] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I9" t="str">
         <v>-</v>
@@ -5995,7 +6071,7 @@
         <v>-</v>
       </c>
       <c r="L9" t="str">
-        <v>Verifica que la expresión [N14] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N14] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="10">
@@ -6012,7 +6088,7 @@
         <v>N15</v>
       </c>
       <c r="E10" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F10" t="str">
         <v>0</v>
@@ -6021,7 +6097,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H10" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N15. La expresión indica que [N15] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N15 | La expresión indica que [N15] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I10" t="str">
         <v>-</v>
@@ -6033,7 +6109,7 @@
         <v>-</v>
       </c>
       <c r="L10" t="str">
-        <v>Verifica que la expresión [N15] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N15] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="11">
@@ -6050,7 +6126,7 @@
         <v>N16</v>
       </c>
       <c r="E11" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F11" t="str">
         <v>0</v>
@@ -6059,7 +6135,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H11" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N16. La expresión indica que [N16] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | N16 | La expresión indica que [N16] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I11" t="str">
         <v>-</v>
@@ -6071,7 +6147,7 @@
         <v>-</v>
       </c>
       <c r="L11" t="str">
-        <v>Verifica que la expresión [N16] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [N16] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="12">
@@ -6088,7 +6164,7 @@
         <v>O31</v>
       </c>
       <c r="E12" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F12" t="str">
         <v>0</v>
@@ -6097,7 +6173,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H12" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | O31. La expresión indica que [O31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | O31 | La expresión indica que [O31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I12" t="str">
         <v>-</v>
@@ -6109,7 +6185,7 @@
         <v>-</v>
       </c>
       <c r="L12" t="str">
-        <v>Verifica que la expresión [O31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [O31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="13">
@@ -6126,7 +6202,7 @@
         <v>O32</v>
       </c>
       <c r="E13" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F13" t="str">
         <v>0</v>
@@ -6135,7 +6211,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H13" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | O32. La expresión indica que [O32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | O32 | La expresión indica que [O32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I13" t="str">
         <v>-</v>
@@ -6147,7 +6223,7 @@
         <v>-</v>
       </c>
       <c r="L13" t="str">
-        <v>Verifica que la expresión [O32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [O32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="14">
@@ -6164,7 +6240,7 @@
         <v>P31</v>
       </c>
       <c r="E14" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F14" t="str">
         <v>0</v>
@@ -6173,7 +6249,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H14" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | P31. La expresión indica que [P31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | P31 | La expresión indica que [P31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I14" t="str">
         <v>-</v>
@@ -6185,7 +6261,7 @@
         <v>-</v>
       </c>
       <c r="L14" t="str">
-        <v>Verifica que la expresión [P31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [P31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="15">
@@ -6202,7 +6278,7 @@
         <v>P32</v>
       </c>
       <c r="E15" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F15" t="str">
         <v>0</v>
@@ -6211,7 +6287,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H15" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | P32. La expresión indica que [P32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | P32 | La expresión indica que [P32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I15" t="str">
         <v>-</v>
@@ -6223,7 +6299,7 @@
         <v>-</v>
       </c>
       <c r="L15" t="str">
-        <v>Verifica que la expresión [P32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [P32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="16">
@@ -6240,7 +6316,7 @@
         <v>Q31</v>
       </c>
       <c r="E16" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F16" t="str">
         <v>0</v>
@@ -6249,7 +6325,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H16" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Q31. La expresión indica que [Q31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Q31 | La expresión indica que [Q31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I16" t="str">
         <v>-</v>
@@ -6261,7 +6337,7 @@
         <v>-</v>
       </c>
       <c r="L16" t="str">
-        <v>Verifica que la expresión [Q31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [Q31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="17">
@@ -6278,7 +6354,7 @@
         <v>Q32</v>
       </c>
       <c r="E17" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F17" t="str">
         <v>0</v>
@@ -6287,7 +6363,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H17" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Q32. La expresión indica que [Q32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Q32 | La expresión indica que [Q32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I17" t="str">
         <v>-</v>
@@ -6299,7 +6375,7 @@
         <v>-</v>
       </c>
       <c r="L17" t="str">
-        <v>Verifica que la expresión [Q32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [Q32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="18">
@@ -6316,7 +6392,7 @@
         <v>R31</v>
       </c>
       <c r="E18" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F18" t="str">
         <v>0</v>
@@ -6325,7 +6401,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H18" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | R31. La expresión indica que [R31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | R31 | La expresión indica que [R31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I18" t="str">
         <v>-</v>
@@ -6337,7 +6413,7 @@
         <v>-</v>
       </c>
       <c r="L18" t="str">
-        <v>Verifica que la expresión [R31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [R31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="19">
@@ -6354,7 +6430,7 @@
         <v>R32</v>
       </c>
       <c r="E19" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F19" t="str">
         <v>0</v>
@@ -6363,7 +6439,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H19" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | R32. La expresión indica que [R32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | R32 | La expresión indica que [R32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I19" t="str">
         <v>-</v>
@@ -6375,7 +6451,7 @@
         <v>-</v>
       </c>
       <c r="L19" t="str">
-        <v>Verifica que la expresión [R32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [R32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="20">
@@ -6392,7 +6468,7 @@
         <v>S31</v>
       </c>
       <c r="E20" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F20" t="str">
         <v>0</v>
@@ -6401,7 +6477,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H20" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | S31. La expresión indica que [S31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | S31 | La expresión indica que [S31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I20" t="str">
         <v>-</v>
@@ -6413,7 +6489,7 @@
         <v>-</v>
       </c>
       <c r="L20" t="str">
-        <v>Verifica que la expresión [S31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [S31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="21">
@@ -6430,7 +6506,7 @@
         <v>S32</v>
       </c>
       <c r="E21" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F21" t="str">
         <v>0</v>
@@ -6439,7 +6515,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H21" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | S32. La expresión indica que [S32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | S32 | La expresión indica que [S32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I21" t="str">
         <v>-</v>
@@ -6451,7 +6527,7 @@
         <v>-</v>
       </c>
       <c r="L21" t="str">
-        <v>Verifica que la expresión [S32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [S32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="22">
@@ -6468,7 +6544,7 @@
         <v>T31</v>
       </c>
       <c r="E22" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F22" t="str">
         <v>0</v>
@@ -6477,7 +6553,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H22" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | T31. La expresión indica que [T31] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | T31 | La expresión indica que [T31] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I22" t="str">
         <v>-</v>
@@ -6489,7 +6565,7 @@
         <v>-</v>
       </c>
       <c r="L22" t="str">
-        <v>Verifica que la expresión [T31] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [T31] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="23">
@@ -6506,7 +6582,7 @@
         <v>T32</v>
       </c>
       <c r="E23" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F23" t="str">
         <v>0</v>
@@ -6515,7 +6591,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H23" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | T32. La expresión indica que [T32] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | T32 | La expresión indica que [T32] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I23" t="str">
         <v>-</v>
@@ -6527,7 +6603,7 @@
         <v>-</v>
       </c>
       <c r="L23" t="str">
-        <v>Verifica que la expresión [T32] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [T32] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="24">
@@ -6541,19 +6617,19 @@
         <v>CELDA</v>
       </c>
       <c r="D24" t="str">
-        <v>A05!C89</v>
+        <v>SUM(C19:C26, F36:F38)</v>
       </c>
       <c r="E24" t="str">
         <v>==</v>
       </c>
       <c r="F24" t="str">
-        <v>SUM(C19:C26, F36:F38)</v>
+        <v>A05!C89</v>
       </c>
       <c r="G24" t="str">
         <v>ERROR</v>
       </c>
       <c r="H24" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | A05, C89, C19, C26, F36, F38. La expresión indica que [A05!C89] debe ser igual a [SUM(C19:C26, F36:F38)].</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | C19, C26, F36, F38 | REM A05 | SECCIÓN E:  INGRESOS  A CONTROL DE SALUD DE RECIÉN NACIDOS | C89. La expresión indica que [SUM(C19:C26, F36:F38)] debe ser igual a [A05!C89].</v>
       </c>
       <c r="I24" t="str">
         <v>-</v>
@@ -6565,7 +6641,7 @@
         <v>-</v>
       </c>
       <c r="L24" t="str">
-        <v>Compara [A05!C89] sea igual a la suma del rango [SUM(C19:C26, F36:F38)].</v>
+        <v>Comparación cross-sheet: verifica que [SUM(C19:C26, F36:F38)] sea igual a [A05!C89] (referencia a otra hoja del libro).</v>
       </c>
     </row>
     <row r="25">
@@ -6591,7 +6667,7 @@
         <v>ERROR</v>
       </c>
       <c r="H25" t="str">
-        <v>REM A01 | SECCIÓN D: CONTROL DE SALUD INTEGRAL DE ADOLESCENTES (incluidos en sección B) | C74, T36, T38. La expresión indica que [C74] debe ser menor o igual a [T36:T38].</v>
+        <v>REM A01 | SECCIÓN D: CONTROL DE SALUD INTEGRAL DE ADOLESCENTES (incluidos en sección B) | C74 | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | T36, T38. La expresión indica que [C74] debe ser menor o igual a [T36:T38].</v>
       </c>
       <c r="I25" t="str">
         <v>-</v>
@@ -6629,7 +6705,7 @@
         <v>ERROR</v>
       </c>
       <c r="H26" t="str">
-        <v>REM A01 | SECCIÓN D: CONTROL DE SALUD INTEGRAL DE ADOLESCENTES (incluidos en sección B) | F74, U36, U38. La expresión indica que [F74] debe ser menor o igual a [U36:U38].</v>
+        <v>REM A01 | SECCIÓN D: CONTROL DE SALUD INTEGRAL DE ADOLESCENTES (incluidos en sección B) | F74 | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | U36, U38. La expresión indica que [F74] debe ser menor o igual a [U36:U38].</v>
       </c>
       <c r="I26" t="str">
         <v>-</v>
@@ -6658,7 +6734,7 @@
         <v>F36</v>
       </c>
       <c r="E27" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F27" t="str">
         <v>0</v>
@@ -6667,7 +6743,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H27" t="str">
-        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | F36. La expresión indica que [F36] la celda no debe contener datos.</v>
+        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | F36 | La expresión indica que [F36] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I27" t="str">
         <v>-</v>
@@ -6679,7 +6755,7 @@
         <v>-</v>
       </c>
       <c r="L27" t="str">
-        <v>Verifica que la expresión [F36] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [F36] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="28">
@@ -6705,7 +6781,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H28" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | A03, L20, M20, O36, O37. La expresión indica que [A03!L20 + A03!M20] debe ser igual a [O36:O37].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | L20, M20 | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | O36, O37. La expresión indica que [A03!L20 + A03!M20] debe ser igual a [O36:O37].</v>
       </c>
       <c r="I28" t="str">
         <v>-</v>
@@ -6743,7 +6819,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H29" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | A03, N20, O20, A01, P36, P37. La expresión indica que [A03!N20 + A03!O20] debe ser igual a [A01!P36 + A01!P37].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | N20, O20 | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | P36, P37. La expresión indica que [A03!N20 + A03!O20] debe ser igual a [A01!P36 + A01!P37].</v>
       </c>
       <c r="I29" t="str">
         <v>-</v>
@@ -6844,7 +6920,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | B11, B21. La expresión indica que [B11] debe ser igual a [B21].</v>
+        <v>REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | B11 | REM A02 | SECCIÓN B: EMP SEGÚN RESULTADO DEL ESTADO NUTRICIONAL | B21. La expresión indica que [B11] debe ser igual a [B21].</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -6882,7 +6958,7 @@
         <v>ERROR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | C11, C21. La expresión indica que [C11] debe ser igual a [C21].</v>
+        <v>REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | C11 | REM A02 | SECCIÓN B: EMP SEGÚN RESULTADO DEL ESTADO NUTRICIONAL | C21. La expresión indica que [C11] debe ser igual a [C21].</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -6920,7 +6996,7 @@
         <v>ERROR</v>
       </c>
       <c r="H4" t="str">
-        <v>REM A02 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A03, C108, C110, B11. La expresión indica que [A03!C108 + A03!C110] debe ser igual a [B11].</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C108, C110 | REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | B11. La expresión indica que [A03!C108 + A03!C110] debe ser igual a [B11].</v>
       </c>
       <c r="I4" t="str">
         <v>-</v>
@@ -6958,7 +7034,7 @@
         <v>ERROR</v>
       </c>
       <c r="H5" t="str">
-        <v>REM A02 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A03, C113, E11, F11. La expresión indica que [A03!C113] debe ser igual a [E11 + F11].</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C113 | REM A02 | SECCIÓN A: EMP REALIZADO POR PROFESIONAL | E11, F11. La expresión indica que [A03!C113] debe ser igual a [E11 + F11].</v>
       </c>
       <c r="I5" t="str">
         <v>-</v>
@@ -7059,7 +7135,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C20, C21, C36. La expresión indica que [C20] debe ser igual a [C21:C36].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C20 | REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C21, C36. La expresión indica que [C20] debe ser igual a [C21:C36].</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -7097,7 +7173,7 @@
         <v>ERROR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | C13, C14, C15. La expresión indica que [C13] debe ser igual a [C14:C15].</v>
+        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | C13 | REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | C14, C15. La expresión indica que [C13] debe ser igual a [C14:C15].</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -7135,7 +7211,7 @@
         <v>ERROR</v>
       </c>
       <c r="H4" t="str">
-        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | C54, C55, C57. La expresión indica que [C54] debe ser igual a [C55:C57].</v>
+        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | C54 | REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | C55, C57. La expresión indica que [C54] debe ser igual a [C55:C57].</v>
       </c>
       <c r="I4" t="str">
         <v>-</v>
@@ -7173,7 +7249,7 @@
         <v>ERROR</v>
       </c>
       <c r="H5" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C22, B46. La expresión indica que [C22] debe ser igual a [B46].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C22 | REM A03 | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | B46. La expresión indica que [C22] debe ser igual a [B46].</v>
       </c>
       <c r="I5" t="str">
         <v>-</v>
@@ -7211,7 +7287,7 @@
         <v>ERROR</v>
       </c>
       <c r="H6" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C23, B47. La expresión indica que [C23] debe ser igual a [B47].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C23 | REM A03 | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | B47. La expresión indica que [C23] debe ser igual a [B47].</v>
       </c>
       <c r="I6" t="str">
         <v>-</v>
@@ -7249,7 +7325,7 @@
         <v>ERROR</v>
       </c>
       <c r="H7" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C24, B48. La expresión indica que [C24] debe ser igual a [B48].</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | C24 | REM A03 | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | B48. La expresión indica que [C24] debe ser igual a [B48].</v>
       </c>
       <c r="I7" t="str">
         <v>-</v>
@@ -7287,7 +7363,7 @@
         <v>ERROR</v>
       </c>
       <c r="H8" t="str">
-        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | B86, A05, C11. La expresión indica que [B86] debe ser igual a [A05!C11].</v>
+        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | B86 | REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | C11. La expresión indica que [B86] debe ser igual a [A05!C11].</v>
       </c>
       <c r="I8" t="str">
         <v>-</v>
@@ -7325,7 +7401,7 @@
         <v>ERROR</v>
       </c>
       <c r="H9" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | C92, A01, H36, H37. La expresión indica que [C92] debe ser menor o igual a [A01!(H36:H37)].</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | C92 | REM A03 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A01, H36, H37. La expresión indica que [C92] debe ser menor o igual a [A01!(H36:H37)].</v>
       </c>
       <c r="I9" t="str">
         <v>-</v>
@@ -7363,7 +7439,7 @@
         <v>ERROR</v>
       </c>
       <c r="H10" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | C93, A01, L36, L37. La expresión indica que [C93] debe ser menor o igual a [A01!(L36:L37)].</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | C93 | REM A03 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A01, L36, L37. La expresión indica que [C93] debe ser menor o igual a [A01!(L36:L37)].</v>
       </c>
       <c r="I10" t="str">
         <v>-</v>
@@ -7401,7 +7477,7 @@
         <v>ERROR</v>
       </c>
       <c r="H11" t="str">
-        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | C97, A01, T36, U38. La expresión indica que [C97] debe ser igual a [A01!(T36:U38)].</v>
+        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | C97 | REM A03 | SECCIÓN A: APLICACIÓN DE INSTRUMENTO Y RESULTADO EN EL NIÑO (A) | A01, T36, U38. La expresión indica que [C97] debe ser igual a [A01!(T36:U38)].</v>
       </c>
       <c r="I11" t="str">
         <v>-</v>
@@ -7439,7 +7515,7 @@
         <v>ERROR</v>
       </c>
       <c r="H12" t="str">
-        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C108, C114, C115, C117. La expresión indica que [C108:C114] debe ser igual a [C115:C117].</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C108, C114 | REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | C115, C117. La expresión indica que [C108:C114] debe ser igual a [C115:C117].</v>
       </c>
       <c r="I12" t="str">
         <v>-</v>
@@ -7477,7 +7553,7 @@
         <v>ERROR</v>
       </c>
       <c r="H13" t="str">
-        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | C213, C214, C215. La expresión indica que [C213] debe ser igual a [C214+C215].</v>
+        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | C213 | REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | C214, C215. La expresión indica que [C213] debe ser igual a [C214+C215].</v>
       </c>
       <c r="I13" t="str">
         <v>-</v>
@@ -7515,7 +7591,7 @@
         <v>ERROR</v>
       </c>
       <c r="H14" t="str">
-        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | C61, C66, C67. La expresión indica que [C61:C66] debe ser igual a [C67].</v>
+        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | C61, C66 | REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | C67. La expresión indica que [C61:C66] debe ser igual a [C67].</v>
       </c>
       <c r="I14" t="str">
         <v>-</v>
@@ -7616,7 +7692,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A04 | SECCIÓN B: CONSULTAS DE PROFESIONALES NO MÉDICOS | B39, B41, B135, B137. La expresión indica que [B39:B41] debe ser igual a [B135:B137].</v>
+        <v>REM A04 | SECCIÓN B: CONSULTAS DE PROFESIONALES NO MÉDICOS | B39, B41 | REM A04 | SECCIÓN K CLASIFICACIÓN DE CONSULTA NUTRICIONAL POR GRUPO DE EDAD (Incluidas en sección B) | B135, B137. La expresión indica que [B39:B41] debe ser igual a [B135:B137].</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -7654,7 +7730,7 @@
         <v>ERROR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | C141, C143, C146, C149. La expresión indica que [C141:C143] debe ser igual a [C146:C149].</v>
+        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | C141, C143 | REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | C146, C149. La expresión indica que [C141:C143] debe ser igual a [C146:C149].</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -7692,7 +7768,7 @@
         <v>ERROR</v>
       </c>
       <c r="H4" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C114, D114, E114, F114. La expresión indica que [C114+D114] debe ser igual a [E114+F114].</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C114, D114 | REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | E114, F114. La expresión indica que [C114+D114] debe ser igual a [E114+F114].</v>
       </c>
       <c r="I4" t="str">
         <v>-</v>
@@ -7730,7 +7806,7 @@
         <v>ERROR</v>
       </c>
       <c r="H5" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C115, D115, E115, F115. La expresión indica que [C115+D115] debe ser igual a [E115+F115].</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C115, D115 | REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | E115, F115. La expresión indica que [C115+D115] debe ser igual a [E115+F115].</v>
       </c>
       <c r="I5" t="str">
         <v>-</v>
@@ -7768,7 +7844,7 @@
         <v>ERROR</v>
       </c>
       <c r="H6" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C116, D116, E116, F116. La expresión indica que [C116+D116] debe ser igual a [E116+F116].</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | C116, D116 | REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | E116, F116. La expresión indica que [C116+D116] debe ser igual a [E116+F116].</v>
       </c>
       <c r="I6" t="str">
         <v>-</v>
@@ -7806,7 +7882,7 @@
         <v>ERROR</v>
       </c>
       <c r="H7" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | M114, L114. La expresión indica que [M114] debe ser mayor o igual a [L114].</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | M114 | REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | L114. La expresión indica que [M114] debe ser mayor o igual a [L114].</v>
       </c>
       <c r="I7" t="str">
         <v>-</v>
@@ -7898,7 +7974,7 @@
         <v>L11:N14</v>
       </c>
       <c r="E2" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F2" t="str">
         <v>0</v>
@@ -7907,7 +7983,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | L11, N14. La expresión indica que [L11:N14] la celda no debe contener datos.</v>
+        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | L11, N14 | La expresión indica que [L11:N14] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I2" t="str">
         <v>-</v>
@@ -7919,7 +7995,7 @@
         <v>-</v>
       </c>
       <c r="L2" t="str">
-        <v>Verifica que la expresión [L11:N14] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [L11:N14] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="3">
@@ -7945,7 +8021,7 @@
         <v>ERROR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | C119, C120, C127. La expresión indica que [C119] debe ser menor o igual a [C120:C127].</v>
+        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | C119 | REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | C120, C127. La expresión indica que [C119] debe ser menor o igual a [C120:C127].</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -7983,7 +8059,7 @@
         <v>ERROR</v>
       </c>
       <c r="H4" t="str">
-        <v>REM A05 | SECCIÓN J: INGRESOS Y EGRESOS AL PROGRAMA DE PACIENTES CON DEPENDENCIA LEVE, MODERADA Y SEVERA | AF146, AM150, C162. La expresión indica que [AF146:AM150] debe ser estrictamente mayor a [C162].</v>
+        <v>REM A05 | SECCIÓN J: INGRESOS Y EGRESOS AL PROGRAMA DE PACIENTES CON DEPENDENCIA LEVE, MODERADA Y SEVERA | AF146, AM150 | REM A05 | SECCIÓN K: INGRESOS AL PROGRAMA DEL ADULTO MAYOR SEGÚN CONDICIÓN DE FUNCIONALIDAD Y DEPENDENCIA | C162. La expresión indica que [AF146:AM150] debe ser estrictamente mayor a [C162].</v>
       </c>
       <c r="I4" t="str">
         <v>-</v>
@@ -8021,7 +8097,7 @@
         <v>REVISAR</v>
       </c>
       <c r="H5" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C193, C204. La expresión indica que [C193] debe ser igual a [C204].</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C193 | REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C204. La expresión indica que [C193] debe ser igual a [C204].</v>
       </c>
       <c r="I5" t="str">
         <v>-</v>
@@ -8059,7 +8135,7 @@
         <v>ERROR</v>
       </c>
       <c r="H6" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C204, C205, C241. La expresión indica que [C204] debe ser menor o igual a [C205:C241].</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C204 | REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | C205, C241. La expresión indica que [C204] debe ser menor o igual a [C205:C241].</v>
       </c>
       <c r="I6" t="str">
         <v>-</v>
@@ -8151,7 +8227,7 @@
         <v>C61:AL66</v>
       </c>
       <c r="E2" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F2" t="str">
         <v>0</v>
@@ -8160,7 +8236,7 @@
         <v>ERROR</v>
       </c>
       <c r="H2" t="str">
-        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | C61, AL66. La expresión indica que [C61:AL66] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | C61, AL66 | La expresión indica que [C61:AL66] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I2" t="str">
         <v>Tipo: HOSPITAL, SAPU, SUR</v>
@@ -8172,7 +8248,7 @@
         <v>-</v>
       </c>
       <c r="L2" t="str">
-        <v>Verifica que la expresión [C61:AL66] NO contenga datos (sea cero o vacía). | Solo aplica a tipo: HOSPITAL, SAPU, SUR. Excluye códigos: 123000, 123100, 123101, 123102, 123103, 123104, 123105, 123800, 123801, 200085, 200747, 200748, 200749, 200750</v>
+        <v>Verifica que la expresión [C61:AL66] contenga datos (no sea cero ni vacía). | Solo aplica a tipo: HOSPITAL, SAPU, SUR. Excluye códigos: 123000, 123100, 123101, 123102, 123103, 123104, 123105, 123800, 123801, 200085, 200747, 200748, 200749, 200750</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8274,7 @@
         <v>ERROR</v>
       </c>
       <c r="H3" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | B13, B14, B78. La expresión indica que [B13+B14] debe ser igual a [B78].</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | B13, B14 | REM A08 | SECCIÓN B.1: CATEGORIZACIÓN DE PACIENTES DE URGENCIA GINECO OBSTÉTRICA PREVIO A LA ATENCIÓN CLÍNICA POR MATRÓN (A) Y/O MÉDICO GINECO-OBSTETRA (Establecimientos alta, mediana y baja complejidad) | B78. La expresión indica que [B13+B14] debe ser igual a [B78].</v>
       </c>
       <c r="I3" t="str">
         <v>-</v>
@@ -8227,7 +8303,7 @@
         <v>C171:F171</v>
       </c>
       <c r="E4" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F4" t="str">
         <v>0</v>
@@ -8236,7 +8312,7 @@
         <v>ERROR</v>
       </c>
       <c r="H4" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | C171, F171. La expresión indica que [C171:F171] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | C171, F171 | La expresión indica que [C171:F171] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I4" t="str">
         <v>-</v>
@@ -8248,7 +8324,7 @@
         <v>-</v>
       </c>
       <c r="L4" t="str">
-        <v>Verifica que la expresión [C171:F171] NO contenga datos (sea cero o vacía). | Excluye códigos: 123000, 123102, 123101, 123104, 123105, 123311, 200747, 200748, 200749, 200750</v>
+        <v>Verifica que la expresión [C171:F171] contenga datos (no sea cero ni vacía). | Excluye códigos: 123000, 123102, 123101, 123104, 123105, 123311, 200747, 200748, 200749, 200750</v>
       </c>
     </row>
     <row r="5">
@@ -8265,7 +8341,7 @@
         <v>C172:F174</v>
       </c>
       <c r="E5" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F5" t="str">
         <v>0</v>
@@ -8274,7 +8350,7 @@
         <v>ERROR</v>
       </c>
       <c r="H5" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | C172, F174. La expresión indica que [C172:F174] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | C172, F174 | La expresión indica que [C172:F174] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I5" t="str">
         <v>-</v>
@@ -8286,7 +8362,7 @@
         <v>-</v>
       </c>
       <c r="L5" t="str">
-        <v>Verifica que la expresión [C172:F174] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [C172:F174] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="6">
@@ -8303,7 +8379,7 @@
         <v>E178:E183</v>
       </c>
       <c r="E6" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F6" t="str">
         <v>0</v>
@@ -8312,7 +8388,7 @@
         <v>ERROR</v>
       </c>
       <c r="H6" t="str">
-        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | E178, E183. La expresión indica que [E178:E183] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | E178, E183 | La expresión indica que [E178:E183] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I6" t="str">
         <v>-</v>
@@ -8324,7 +8400,7 @@
         <v>-</v>
       </c>
       <c r="L6" t="str">
-        <v>Verifica que la expresión [E178:E183] NO contenga datos (sea cero o vacía). | Excluye tipo: SAMU. Excluye códigos: 123010</v>
+        <v>Verifica que la expresión [E178:E183] contenga datos (no sea cero ni vacía). | Excluye tipo: SAMU. Excluye códigos: 123010</v>
       </c>
     </row>
     <row r="7">
@@ -8341,7 +8417,7 @@
         <v>C161+D161</v>
       </c>
       <c r="E7" t="str">
-        <v>==</v>
+        <v>!=</v>
       </c>
       <c r="F7" t="str">
         <v>0</v>
@@ -8350,7 +8426,7 @@
         <v>ERROR</v>
       </c>
       <c r="H7" t="str">
-        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | C161, D161. La expresión indica que [C161+D161] la celda no debe contener datos.</v>
+        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | C161, D161 | La expresión indica que [C161+D161] la celda debe contener datos (distinto de cero).</v>
       </c>
       <c r="I7" t="str">
         <v>-</v>
@@ -8362,7 +8438,7 @@
         <v>-</v>
       </c>
       <c r="L7" t="str">
-        <v>Verifica que la expresión [C161+D161] NO contenga datos (sea cero o vacía).</v>
+        <v>Verifica que la expresión [C161+D161] contenga datos (no sea cero ni vacía).</v>
       </c>
     </row>
     <row r="8">
@@ -8388,7 +8464,7 @@
         <v>ERROR</v>
       </c>
       <c r="H8" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | B13, AS13. La expresión indica que [B13] debe ser estrictamente menor a [AS13].</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | B13 | REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | AS13. La expresión indica que [B13] debe ser estrictamente menor a [AS13].</v>
       </c>
       <c r="I8" t="str">
         <v>-</v>
